--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_43.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3447424.806138312</v>
+        <v>3448528.192956976</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13604525.51577222</v>
+        <v>13604525.51577221</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13604525.51577222</v>
+        <v>13604525.51577221</v>
       </c>
     </row>
     <row r="9">
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.343301935256381</v>
+        <v>3.343301935257416</v>
       </c>
       <c r="H2" t="n">
-        <v>3.769060713577687</v>
+        <v>3.769060713576854</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.953406460792503</v>
       </c>
       <c r="S2" t="n">
-        <v>87.36594612241183</v>
+        <v>85.41253966161939</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1881709204699</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -736,13 +736,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>239.4441949114584</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,22 +778,22 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>133.5184388018132</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S3" t="n">
         <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>374</v>
+        <v>4.46477465147608</v>
       </c>
       <c r="U3" t="n">
         <v>374</v>
       </c>
       <c r="V3" t="n">
-        <v>310.2191416989563</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.51638189435317</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N4" t="n">
         <v>142.7621408454554</v>
@@ -854,7 +854,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>264.9837661807364</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q4" t="n">
         <v>310.286266425598</v>
@@ -903,10 +903,10 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>6.997753761768089</v>
       </c>
       <c r="G5" t="n">
-        <v>5.447406888511135</v>
+        <v>3.3392818347549</v>
       </c>
       <c r="H5" t="n">
         <v>3.727889859306288</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>175.8266534255268</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -988,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>86.92995693142628</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4244990988957</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.5243971659513</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.3848916320019</v>
       </c>
       <c r="S6" t="n">
-        <v>62.40890562498868</v>
+        <v>374</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.456104840155319</v>
       </c>
       <c r="U6" t="n">
-        <v>374</v>
+        <v>0.1956427790546513</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>330.6651090678901</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.5243971659513</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.3848916320019</v>
@@ -1264,13 +1264,13 @@
         <v>4.456104840155319</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1956427790546513</v>
+        <v>107.6959788204272</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1383,10 +1383,10 @@
         <v>81.35435721163935</v>
       </c>
       <c r="H11" t="n">
-        <v>73.87521089296166</v>
+        <v>72.64103056282391</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1.234180330137742</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1447,13 +1447,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>229.637479822776</v>
       </c>
       <c r="D12" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
         <v>18.63624233787687</v>
@@ -1498,22 +1498,22 @@
         <v>131.6204622287622</v>
       </c>
       <c r="T12" t="n">
-        <v>270.8695684438271</v>
+        <v>81.3320010665704</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16097296773393</v>
+        <v>400.1609729677339</v>
       </c>
       <c r="V12" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1617,10 +1617,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.35435721163935</v>
+        <v>82.58853754177711</v>
       </c>
       <c r="H14" t="n">
-        <v>73.87521089296166</v>
+        <v>72.6410305628239</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>208.1738097151335</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>3.988856629744305</v>
+        <v>3.988856629744324</v>
       </c>
       <c r="H15" t="n">
-        <v>3.918106054345685</v>
+        <v>3.918106054345659</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>131.6204622287622</v>
       </c>
       <c r="T15" t="n">
-        <v>81.3320010665704</v>
+        <v>81.33200106657043</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16097296773393</v>
+        <v>400.1609729677339</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
@@ -1747,10 +1747,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>267.9289601433911</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8.981300288926718</v>
+        <v>8.981300288926704</v>
       </c>
       <c r="M16" t="n">
         <v>100.9790376320581</v>
@@ -1811,7 +1811,7 @@
         <v>377.304521423774</v>
       </c>
       <c r="S16" t="n">
-        <v>30.40572560449476</v>
+        <v>30.40572560449478</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>72.64103056282391</v>
       </c>
       <c r="I17" t="n">
-        <v>1.234180330137742</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>259.5338832361016</v>
       </c>
       <c r="U17" t="n">
-        <v>328.1090553425805</v>
+        <v>329.3432356727183</v>
       </c>
       <c r="V17" t="n">
         <v>308.8510241668239</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>253.0941240235834</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>26.93768689770263</v>
@@ -1981,13 +1981,13 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>267.9289601433911</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2091,10 +2091,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.35435721163932</v>
+        <v>81.35435721163935</v>
       </c>
       <c r="H20" t="n">
-        <v>72.6410305628239</v>
+        <v>72.64103056282391</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>229.6374798227762</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>211.2096645991693</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.988856629744324</v>
+        <v>324.9888566297443</v>
       </c>
       <c r="H21" t="n">
-        <v>3.918106054345659</v>
+        <v>3.918106054345685</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2209,10 +2209,10 @@
         <v>131.6204622287622</v>
       </c>
       <c r="T21" t="n">
-        <v>81.33200106657043</v>
+        <v>81.3320010665704</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16097296773391</v>
+        <v>79.16097296773393</v>
       </c>
       <c r="V21" t="n">
         <v>93.51066719152016</v>
@@ -2224,7 +2224,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>8.981300288926704</v>
+        <v>8.981300288926718</v>
       </c>
       <c r="M22" t="n">
         <v>100.9790376320581</v>
@@ -2285,7 +2285,7 @@
         <v>377.304521423774</v>
       </c>
       <c r="S22" t="n">
-        <v>30.40572560449478</v>
+        <v>30.40572560449476</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>72.64103056282391</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1.234180330137742</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>259.5338832361016</v>
       </c>
       <c r="U23" t="n">
-        <v>329.3432356727183</v>
+        <v>328.1090553425805</v>
       </c>
       <c r="V23" t="n">
         <v>308.8510241668239</v>
@@ -2392,22 +2392,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>229.637479822776</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>3.988856629744305</v>
+        <v>324.9888566297443</v>
       </c>
       <c r="H24" t="n">
         <v>3.918106054345685</v>
@@ -2449,13 +2449,13 @@
         <v>81.3320010665704</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16097296773393</v>
+        <v>400.1609729677339</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>300.9107102870853</v>
       </c>
       <c r="X24" t="n">
         <v>98.86273944538755</v>
@@ -2571,7 +2571,7 @@
         <v>72.64103056282391</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.114980330137729</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5.114980330137827</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>141.8769617721721</v>
@@ -2632,13 +2632,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>359.3568486484087</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
@@ -2650,7 +2650,7 @@
         <v>3.918106054345685</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.2806311743674</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2677,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>369.2034024054848</v>
+        <v>179.6658350282283</v>
       </c>
       <c r="S27" t="n">
         <v>131.6204622287622</v>
       </c>
       <c r="T27" t="n">
-        <v>81.3320010665704</v>
+        <v>402.3320010665704</v>
       </c>
       <c r="U27" t="n">
         <v>79.16097296773393</v>
@@ -2695,7 +2695,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2875,16 +2875,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>208.1738097151336</v>
       </c>
       <c r="G30" t="n">
         <v>3.988856629744324</v>
       </c>
       <c r="H30" t="n">
-        <v>3.918106054345659</v>
+        <v>324.9181060543457</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2920,19 +2920,19 @@
         <v>131.6204622287622</v>
       </c>
       <c r="T30" t="n">
-        <v>81.33200106657043</v>
+        <v>402.3320010665704</v>
       </c>
       <c r="U30" t="n">
         <v>79.16097296773391</v>
       </c>
       <c r="V30" t="n">
-        <v>283.0482345687768</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -3039,13 +3039,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.35435721163935</v>
+        <v>81.35435721163932</v>
       </c>
       <c r="H32" t="n">
-        <v>72.64103056282391</v>
+        <v>72.6410305628239</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5.1149803301378</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>146.9919421023101</v>
+        <v>141.8769617721721</v>
       </c>
       <c r="T32" t="n">
         <v>259.5338832361016</v>
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>229.6374798227761</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.988856629744305</v>
+        <v>3.988856629744324</v>
       </c>
       <c r="H33" t="n">
-        <v>3.918106054345685</v>
+        <v>193.4556734316023</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3154,16 +3154,16 @@
         <v>179.6658350282283</v>
       </c>
       <c r="S33" t="n">
-        <v>452.6204622287622</v>
+        <v>131.6204622287622</v>
       </c>
       <c r="T33" t="n">
-        <v>81.3320010665704</v>
+        <v>81.33200106657043</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16097296773393</v>
+        <v>79.16097296773391</v>
       </c>
       <c r="V33" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
         <v>111.3731429098285</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>8.981300288926718</v>
+        <v>8.981300288926704</v>
       </c>
       <c r="M34" t="n">
         <v>100.9790376320581</v>
@@ -3233,7 +3233,7 @@
         <v>377.304521423774</v>
       </c>
       <c r="S34" t="n">
-        <v>30.40572560449476</v>
+        <v>30.40572560449478</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3343,13 +3343,13 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>89.74278806840863</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -3358,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>324.9181060543457</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>191.2806311743674</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>155.6658350282283</v>
+        <v>500.6658350282283</v>
       </c>
       <c r="S36" t="n">
         <v>107.6204622287622</v>
@@ -3403,10 +3403,10 @@
         <v>69.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>350.9171937495242</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>54.39139276613435</v>
@@ -3586,7 +3586,7 @@
         <v>2.937686897702633</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.9181060543457</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,16 +3628,16 @@
         <v>155.6658350282283</v>
       </c>
       <c r="S39" t="n">
-        <v>197.3632502971709</v>
+        <v>219.7730470209124</v>
       </c>
       <c r="T39" t="n">
         <v>57.33200106657042</v>
       </c>
       <c r="U39" t="n">
-        <v>400.1609729677339</v>
+        <v>55.16097296773392</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>432.3731429098285</v>
@@ -3789,7 +3789,7 @@
         <v>141.8769617721721</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>259.5338832361016</v>
       </c>
       <c r="U41" t="n">
         <v>328.1090553425805</v>
@@ -3801,10 +3801,10 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>198.3010970269073</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>190.3174326828064</v>
+        <v>129.0846464736119</v>
       </c>
     </row>
     <row r="42">
@@ -3826,7 +3826,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>3.988856629744324</v>
@@ -3835,7 +3835,7 @@
         <v>3.918106054345659</v>
       </c>
       <c r="I42" t="n">
-        <v>191.2806311743674</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,22 +3859,22 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>77.25571792066825</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>500.6658350282283</v>
+        <v>368.8295631906925</v>
       </c>
       <c r="S42" t="n">
-        <v>131.6204622287622</v>
+        <v>452.6204622287622</v>
       </c>
       <c r="T42" t="n">
         <v>81.33200106657043</v>
       </c>
       <c r="U42" t="n">
-        <v>400.1609729677339</v>
+        <v>79.16097296773391</v>
       </c>
       <c r="V42" t="n">
-        <v>335.1380462589415</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
         <v>111.3731429098285</v>
@@ -3883,7 +3883,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.80212596851866</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>128.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>89.33915573984979</v>
+        <v>28.10636953065523</v>
       </c>
       <c r="E44" t="n">
         <v>83.36328960686865</v>
@@ -4038,10 +4038,10 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>271.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4054,10 +4054,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>216.101415060174</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -4066,7 +4066,7 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.988856629744305</v>
+        <v>324.9888566297443</v>
       </c>
       <c r="H45" t="n">
         <v>3.918106054345685</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>368.8295631906855</v>
+        <v>179.6658350282283</v>
       </c>
       <c r="S45" t="n">
-        <v>452.6204622287622</v>
+        <v>131.6204622287622</v>
       </c>
       <c r="T45" t="n">
         <v>81.3320010665704</v>
       </c>
       <c r="U45" t="n">
-        <v>400.1609729677339</v>
+        <v>79.16097296773393</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.8684999460185</v>
+        <v>106.8684999460187</v>
       </c>
       <c r="C2" t="n">
-        <v>56.89417848844885</v>
+        <v>56.89417848844905</v>
       </c>
       <c r="D2" t="n">
-        <v>46.45058683203492</v>
+        <v>46.45058683203512</v>
       </c>
       <c r="E2" t="n">
-        <v>42.04322359277366</v>
+        <v>42.04322359277386</v>
       </c>
       <c r="F2" t="n">
-        <v>37.10420469579199</v>
+        <v>37.10420469579219</v>
       </c>
       <c r="G2" t="n">
-        <v>33.72713203391686</v>
+        <v>33.72713203391601</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,31 +4321,31 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>452.3245884924623</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L2" t="n">
-        <v>517.0145614572864</v>
+        <v>452.4242787922349</v>
       </c>
       <c r="M2" t="n">
-        <v>887.2745614572864</v>
+        <v>452.4242787922349</v>
       </c>
       <c r="N2" t="n">
-        <v>1257.534561457286</v>
+        <v>822.6842787922349</v>
       </c>
       <c r="O2" t="n">
-        <v>1257.534561457286</v>
+        <v>822.6842787922349</v>
       </c>
       <c r="P2" t="n">
-        <v>1316.198767846158</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.026862160816</v>
       </c>
       <c r="S2" t="n">
         <v>1407.751569573321</v>
@@ -4354,19 +4354,19 @@
         <v>1221.021277892776</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3160547407863</v>
+        <v>969.3160547407864</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1433030571258</v>
+        <v>737.1433030571259</v>
       </c>
       <c r="W2" t="n">
-        <v>496.3620141874817</v>
+        <v>496.3620141874819</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1379399847871</v>
+        <v>302.1379399847872</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.6960887900331</v>
+        <v>189.6960887900333</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.1199146314645</v>
+        <v>848.3448268129262</v>
       </c>
       <c r="C3" t="n">
-        <v>30.1199146314645</v>
+        <v>483.5974405043208</v>
       </c>
       <c r="D3" t="n">
-        <v>30.1199146314645</v>
+        <v>483.5974405043208</v>
       </c>
       <c r="E3" t="n">
-        <v>30.1199146314645</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="F3" t="n">
-        <v>30.1199146314645</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="G3" t="n">
-        <v>30.1199146314645</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="H3" t="n">
-        <v>30.1199146314645</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="I3" t="n">
         <v>30.1199146314645</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.738421006376</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.871311105555</v>
+        <v>1361.132890099178</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.791656100326</v>
+        <v>1298.053235093949</v>
       </c>
       <c r="T3" t="n">
-        <v>774.0138783225477</v>
+        <v>1293.543361708619</v>
       </c>
       <c r="U3" t="n">
-        <v>396.2361005447699</v>
+        <v>915.7655839308416</v>
       </c>
       <c r="V3" t="n">
-        <v>82.88343216198578</v>
+        <v>901.1083443434475</v>
       </c>
       <c r="W3" t="n">
-        <v>50.18328780862363</v>
+        <v>868.4081999900853</v>
       </c>
       <c r="X3" t="n">
-        <v>30.1199146314645</v>
+        <v>848.3448268129262</v>
       </c>
       <c r="Y3" t="n">
-        <v>30.1199146314645</v>
+        <v>848.3448268129262</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>569.8148679199701</v>
+        <v>748.6427910636701</v>
       </c>
       <c r="C4" t="n">
-        <v>695.8168737384059</v>
+        <v>874.6447968821059</v>
       </c>
       <c r="D4" t="n">
-        <v>809.136017863406</v>
+        <v>874.6447968821059</v>
       </c>
       <c r="E4" t="n">
-        <v>809.136017863406</v>
+        <v>874.6447968821059</v>
       </c>
       <c r="F4" t="n">
-        <v>809.136017863406</v>
+        <v>874.6447968821059</v>
       </c>
       <c r="G4" t="n">
-        <v>809.136017863406</v>
+        <v>874.6447968821059</v>
       </c>
       <c r="H4" t="n">
-        <v>809.136017863406</v>
+        <v>1011.181257449721</v>
       </c>
       <c r="I4" t="n">
-        <v>879.4532726931805</v>
+        <v>1011.181257449721</v>
       </c>
       <c r="J4" t="n">
-        <v>1249.71327269318</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="K4" t="n">
         <v>1381.441257449721</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.37478771712392</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>259.2361373677321</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U4" t="n">
-        <v>259.2361373677321</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="V4" t="n">
-        <v>458.057530253678</v>
+        <v>465.3425721249604</v>
       </c>
       <c r="W4" t="n">
-        <v>458.057530253678</v>
+        <v>637.2334903846378</v>
       </c>
       <c r="X4" t="n">
-        <v>458.057530253678</v>
+        <v>637.2334903846378</v>
       </c>
       <c r="Y4" t="n">
-        <v>458.057530253678</v>
+        <v>748.6427910636701</v>
       </c>
     </row>
     <row r="5">
@@ -4546,7 +4546,7 @@
         <v>44.12699540992857</v>
       </c>
       <c r="F5" t="n">
-        <v>39.1879765129469</v>
+        <v>37.05855726672848</v>
       </c>
       <c r="G5" t="n">
         <v>33.6855453124306</v>
@@ -4558,25 +4558,25 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>30.35747929474751</v>
       </c>
       <c r="K5" t="n">
-        <v>452.8308466331658</v>
+        <v>400.6174792947475</v>
       </c>
       <c r="L5" t="n">
-        <v>518.1488775879398</v>
+        <v>465.9355102495214</v>
       </c>
       <c r="M5" t="n">
-        <v>518.1488775879398</v>
+        <v>836.1955102495214</v>
       </c>
       <c r="N5" t="n">
-        <v>518.1488775879398</v>
+        <v>1066.503479088516</v>
       </c>
       <c r="O5" t="n">
-        <v>888.4088775879397</v>
+        <v>1436.763479088516</v>
       </c>
       <c r="P5" t="n">
-        <v>1258.66887758794</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>329.2679353841636</v>
+        <v>553.6561117650904</v>
       </c>
       <c r="C6" t="n">
-        <v>329.2679353841636</v>
+        <v>553.6561117650904</v>
       </c>
       <c r="D6" t="n">
-        <v>329.2679353841636</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E6" t="n">
-        <v>329.2679353841636</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
-        <v>329.2679353841636</v>
+        <v>29.92</v>
       </c>
       <c r="G6" t="n">
-        <v>329.2679353841636</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>241.4598980796927</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1496</v>
       </c>
       <c r="Q6" t="n">
-        <v>1350.015760438433</v>
+        <v>1496</v>
       </c>
       <c r="R6" t="n">
-        <v>1215.283546668734</v>
+        <v>1361.267786230301</v>
       </c>
       <c r="S6" t="n">
-        <v>1152.244248057635</v>
+        <v>983.4900084525234</v>
       </c>
       <c r="T6" t="n">
-        <v>774.4664702798568</v>
+        <v>978.9888924523665</v>
       </c>
       <c r="U6" t="n">
-        <v>396.688692502079</v>
+        <v>978.7912734836244</v>
       </c>
       <c r="V6" t="n">
-        <v>382.0314529146849</v>
+        <v>964.1340338962303</v>
       </c>
       <c r="W6" t="n">
-        <v>349.3313085613228</v>
+        <v>931.4338895428682</v>
       </c>
       <c r="X6" t="n">
-        <v>329.2679353841636</v>
+        <v>553.6561117650904</v>
       </c>
       <c r="Y6" t="n">
-        <v>329.2679353841636</v>
+        <v>553.6561117650904</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>838.7103217055552</v>
+        <v>592.9864068889785</v>
       </c>
       <c r="C7" t="n">
-        <v>964.712327523991</v>
+        <v>592.9864068889785</v>
       </c>
       <c r="D7" t="n">
-        <v>964.712327523991</v>
+        <v>706.3055510139786</v>
       </c>
       <c r="E7" t="n">
-        <v>1009.639387017531</v>
+        <v>824.1344552253917</v>
       </c>
       <c r="F7" t="n">
-        <v>1009.639387017531</v>
+        <v>824.1344552253917</v>
       </c>
       <c r="G7" t="n">
-        <v>1009.639387017531</v>
+        <v>977.7266866860474</v>
       </c>
       <c r="H7" t="n">
-        <v>1009.639387017531</v>
+        <v>1021.247640046219</v>
       </c>
       <c r="I7" t="n">
-        <v>1009.639387017531</v>
+        <v>1247.963989146236</v>
       </c>
       <c r="J7" t="n">
-        <v>1379.899387017531</v>
+        <v>1247.963989146236</v>
       </c>
       <c r="K7" t="n">
         <v>1379.899387017531</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.40589968433704</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>70.40589968433704</v>
+        <v>218.7889775194606</v>
       </c>
       <c r="U7" t="n">
-        <v>316.9672195357384</v>
+        <v>218.7889775194606</v>
       </c>
       <c r="V7" t="n">
-        <v>515.7886124216843</v>
+        <v>218.7889775194606</v>
       </c>
       <c r="W7" t="n">
-        <v>687.6795306813617</v>
+        <v>218.7889775194606</v>
       </c>
       <c r="X7" t="n">
-        <v>838.7103217055552</v>
+        <v>369.8197685436542</v>
       </c>
       <c r="Y7" t="n">
-        <v>838.7103217055552</v>
+        <v>481.2290692226864</v>
       </c>
     </row>
     <row r="8">
@@ -4798,22 +4798,22 @@
         <v>30.35747929474751</v>
       </c>
       <c r="K8" t="n">
-        <v>400.6174792947475</v>
+        <v>83.00832592791333</v>
       </c>
       <c r="L8" t="n">
-        <v>770.8774792947474</v>
+        <v>453.2683259279133</v>
       </c>
       <c r="M8" t="n">
-        <v>770.8774792947476</v>
+        <v>823.5283259279133</v>
       </c>
       <c r="N8" t="n">
-        <v>1125.546288566794</v>
+        <v>823.5283259279133</v>
       </c>
       <c r="O8" t="n">
+        <v>1066.503479088516</v>
+      </c>
+      <c r="P8" t="n">
         <v>1125.74</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>746.1195952961839</v>
+        <v>394.6673863086054</v>
       </c>
       <c r="C9" t="n">
-        <v>381.3722089875785</v>
+        <v>29.92</v>
       </c>
       <c r="D9" t="n">
         <v>29.92</v>
@@ -4883,43 +4883,43 @@
         <v>719.1893684309202</v>
       </c>
       <c r="M9" t="n">
-        <v>861.3831101737794</v>
+        <v>858.5689698052438</v>
       </c>
       <c r="N9" t="n">
-        <v>1052.26174421531</v>
+        <v>1049.447603846774</v>
       </c>
       <c r="O9" t="n">
-        <v>1343.995432880161</v>
+        <v>1341.181292511625</v>
       </c>
       <c r="P9" t="n">
         <v>1496</v>
       </c>
       <c r="Q9" t="n">
-        <v>1350.015760438433</v>
+        <v>1496</v>
       </c>
       <c r="R9" t="n">
-        <v>1215.283546668734</v>
+        <v>1361.267786230301</v>
       </c>
       <c r="S9" t="n">
-        <v>1152.244248057635</v>
+        <v>1298.228487619202</v>
       </c>
       <c r="T9" t="n">
-        <v>1147.743132057478</v>
+        <v>1293.727371619045</v>
       </c>
       <c r="U9" t="n">
-        <v>1147.545513088736</v>
+        <v>1184.943554628714</v>
       </c>
       <c r="V9" t="n">
-        <v>1132.888273501342</v>
+        <v>1170.28631504132</v>
       </c>
       <c r="W9" t="n">
-        <v>1100.188129147979</v>
+        <v>792.5085372635424</v>
       </c>
       <c r="X9" t="n">
-        <v>1080.12475597082</v>
+        <v>772.4451640863832</v>
       </c>
       <c r="Y9" t="n">
-        <v>1080.12475597082</v>
+        <v>772.4451640863832</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>201.8109182596774</v>
+        <v>749.0873841470038</v>
       </c>
       <c r="C10" t="n">
-        <v>327.8129240781132</v>
+        <v>875.0893899654396</v>
       </c>
       <c r="D10" t="n">
-        <v>441.1320682031132</v>
+        <v>988.4085340904397</v>
       </c>
       <c r="E10" t="n">
-        <v>558.9609724145263</v>
+        <v>1106.237438301853</v>
       </c>
       <c r="F10" t="n">
-        <v>683.3219450064618</v>
+        <v>1230.598410893788</v>
       </c>
       <c r="G10" t="n">
-        <v>836.9141764671175</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="H10" t="n">
-        <v>1008.08149736422</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="I10" t="n">
-        <v>1234.797846464237</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="J10" t="n">
-        <v>1247.963989146236</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="K10" t="n">
-        <v>1379.899387017531</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="L10" t="n">
         <v>1384.190642354444</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.40589968433704</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>70.40589968433704</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>316.9672195357384</v>
       </c>
       <c r="V10" t="n">
-        <v>29.92</v>
+        <v>465.4391282210343</v>
       </c>
       <c r="W10" t="n">
-        <v>201.8109182596774</v>
+        <v>637.3300464807116</v>
       </c>
       <c r="X10" t="n">
-        <v>201.8109182596774</v>
+        <v>637.3300464807116</v>
       </c>
       <c r="Y10" t="n">
-        <v>201.8109182596774</v>
+        <v>637.3300464807116</v>
       </c>
     </row>
     <row r="11">
@@ -5026,28 +5026,28 @@
         <v>126.5414251444057</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>53.16664679811893</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>135.1157830635917</v>
+        <v>449.2777615075377</v>
       </c>
       <c r="K11" t="n">
-        <v>777.6257830635917</v>
+        <v>1091.787761507538</v>
       </c>
       <c r="L11" t="n">
-        <v>1420.135783063592</v>
+        <v>1310.98</v>
       </c>
       <c r="M11" t="n">
-        <v>2062.645783063592</v>
+        <v>1310.98</v>
       </c>
       <c r="N11" t="n">
-        <v>2232.063478208073</v>
+        <v>1310.98</v>
       </c>
       <c r="O11" t="n">
-        <v>2396.546421048315</v>
+        <v>1953.49</v>
       </c>
       <c r="P11" t="n">
         <v>2596</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>492.5794965526277</v>
+        <v>359.7891605700588</v>
       </c>
       <c r="C12" t="n">
-        <v>452.0745344864466</v>
+        <v>127.8321102440223</v>
       </c>
       <c r="D12" t="n">
-        <v>424.8647497412924</v>
+        <v>100.6223254988682</v>
       </c>
       <c r="E12" t="n">
         <v>78.73131820400693</v>
@@ -5141,22 +5141,22 @@
         <v>1944.827012078646</v>
       </c>
       <c r="T12" t="n">
-        <v>1671.221387387912</v>
+        <v>1862.673475647767</v>
       </c>
       <c r="U12" t="n">
-        <v>1591.260808632625</v>
+        <v>1458.470472650056</v>
       </c>
       <c r="V12" t="n">
-        <v>1496.805589247251</v>
+        <v>1039.772829022258</v>
       </c>
       <c r="W12" t="n">
-        <v>1384.307465095909</v>
+        <v>603.0322806284917</v>
       </c>
       <c r="X12" t="n">
-        <v>960.2036878783459</v>
+        <v>503.1709276533527</v>
       </c>
       <c r="Y12" t="n">
-        <v>556.7780386196243</v>
+        <v>423.9877026370553</v>
       </c>
     </row>
     <row r="13">
@@ -5187,10 +5187,10 @@
         <v>1028.019439941366</v>
       </c>
       <c r="I13" t="n">
-        <v>1180.567352683136</v>
+        <v>1189.679156254498</v>
       </c>
       <c r="J13" t="n">
-        <v>1507.490786286407</v>
+        <v>1516.602589857769</v>
       </c>
       <c r="K13" t="n">
         <v>1612.032397272455</v>
@@ -5260,7 +5260,7 @@
         <v>208.717543540001</v>
       </c>
       <c r="G14" t="n">
-        <v>126.5414251444057</v>
+        <v>125.2947783462868</v>
       </c>
       <c r="H14" t="n">
         <v>51.92</v>
@@ -5269,25 +5269,25 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>561.1174722838869</v>
+        <v>135.1157830635917</v>
       </c>
       <c r="K14" t="n">
-        <v>737.8015633894146</v>
+        <v>777.6257830635917</v>
       </c>
       <c r="L14" t="n">
-        <v>956.9938018818768</v>
+        <v>1310.98</v>
       </c>
       <c r="M14" t="n">
-        <v>1200.413216328197</v>
+        <v>1310.98</v>
       </c>
       <c r="N14" t="n">
-        <v>1200.413216328197</v>
+        <v>1310.98</v>
       </c>
       <c r="O14" t="n">
-        <v>1364.896159168438</v>
+        <v>1953.49</v>
       </c>
       <c r="P14" t="n">
-        <v>2007.406159168438</v>
+        <v>2596</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1008.274009054907</v>
+        <v>492.5794965526277</v>
       </c>
       <c r="C15" t="n">
-        <v>643.5266227463019</v>
+        <v>452.0745344864466</v>
       </c>
       <c r="D15" t="n">
-        <v>292.0744137587234</v>
+        <v>424.8647497412924</v>
       </c>
       <c r="E15" t="n">
-        <v>270.1834064638622</v>
+        <v>402.9737424464312</v>
       </c>
       <c r="F15" t="n">
-        <v>59.9068309940303</v>
+        <v>59.90683099403029</v>
       </c>
       <c r="G15" t="n">
-        <v>55.87768288317746</v>
+        <v>55.87768288317744</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5381,19 +5381,19 @@
         <v>1862.673475647767</v>
       </c>
       <c r="U15" t="n">
-        <v>1782.71289689248</v>
+        <v>1458.470472650056</v>
       </c>
       <c r="V15" t="n">
-        <v>1688.257677507106</v>
+        <v>1364.015253264682</v>
       </c>
       <c r="W15" t="n">
-        <v>1575.759553355764</v>
+        <v>1251.51712911334</v>
       </c>
       <c r="X15" t="n">
-        <v>1475.898200380625</v>
+        <v>827.4133518957769</v>
       </c>
       <c r="Y15" t="n">
-        <v>1396.714975364328</v>
+        <v>556.7780386196243</v>
       </c>
     </row>
     <row r="16">
@@ -5403,19 +5403,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>686.6827231319049</v>
+        <v>677.570919560543</v>
       </c>
       <c r="C16" t="n">
-        <v>734.4747289503407</v>
+        <v>725.3629253789787</v>
       </c>
       <c r="D16" t="n">
-        <v>769.5838730753408</v>
+        <v>760.4720695039788</v>
       </c>
       <c r="E16" t="n">
-        <v>809.2027772867538</v>
+        <v>800.0909737153918</v>
       </c>
       <c r="F16" t="n">
-        <v>855.3537498786892</v>
+        <v>846.2419463073272</v>
       </c>
       <c r="G16" t="n">
         <v>922.0615630138847</v>
@@ -5448,31 +5448,31 @@
         <v>819.445771165522</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.7485323517866</v>
+        <v>463.7485323517867</v>
       </c>
       <c r="R16" t="n">
-        <v>82.63285414595431</v>
+        <v>82.63285414595433</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
       </c>
       <c r="T16" t="n">
-        <v>164.447805388313</v>
+        <v>164.4478053883131</v>
       </c>
       <c r="U16" t="n">
-        <v>332.8229826167636</v>
+        <v>323.7111790454016</v>
       </c>
       <c r="V16" t="n">
-        <v>453.4343755027096</v>
+        <v>444.3225719313476</v>
       </c>
       <c r="W16" t="n">
-        <v>547.115293762387</v>
+        <v>538.003490191025</v>
       </c>
       <c r="X16" t="n">
-        <v>619.9360847865805</v>
+        <v>610.8242812152185</v>
       </c>
       <c r="Y16" t="n">
-        <v>653.1353854656128</v>
+        <v>644.0235818942508</v>
       </c>
     </row>
     <row r="17">
@@ -5482,46 +5482,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.6737579821468</v>
+        <v>596.4271111840278</v>
       </c>
       <c r="C17" t="n">
-        <v>467.9014567265973</v>
+        <v>466.6548099284784</v>
       </c>
       <c r="D17" t="n">
-        <v>377.6598852722036</v>
+        <v>376.4132384740846</v>
       </c>
       <c r="E17" t="n">
-        <v>293.4545422349625</v>
+        <v>292.2078954368436</v>
       </c>
       <c r="F17" t="n">
-        <v>208.717543540001</v>
+        <v>207.4708967418821</v>
       </c>
       <c r="G17" t="n">
-        <v>126.5414251444057</v>
+        <v>125.2947783462868</v>
       </c>
       <c r="H17" t="n">
-        <v>53.16664679811893</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>135.1157830635917</v>
+        <v>561.1174722838869</v>
       </c>
       <c r="K17" t="n">
-        <v>311.7998741691194</v>
+        <v>927.3048186672961</v>
       </c>
       <c r="L17" t="n">
-        <v>954.3098741691193</v>
+        <v>1146.497057159758</v>
       </c>
       <c r="M17" t="n">
-        <v>1589.553478208073</v>
+        <v>1789.007057159758</v>
       </c>
       <c r="N17" t="n">
-        <v>2232.063478208073</v>
+        <v>1789.007057159758</v>
       </c>
       <c r="O17" t="n">
-        <v>2396.546421048315</v>
+        <v>1953.49</v>
       </c>
       <c r="P17" t="n">
         <v>2596</v>
@@ -5539,19 +5539,19 @@
         <v>2190.534499991642</v>
       </c>
       <c r="U17" t="n">
-        <v>1859.111211766814</v>
+        <v>1857.864564968695</v>
       </c>
       <c r="V17" t="n">
-        <v>1547.140480285173</v>
+        <v>1545.893833487054</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.561211617549</v>
+        <v>1225.31456481943</v>
       </c>
       <c r="X17" t="n">
-        <v>952.5391576168749</v>
+        <v>951.292510818756</v>
       </c>
       <c r="Y17" t="n">
-        <v>760.2993266241413</v>
+        <v>759.0526798260223</v>
       </c>
     </row>
     <row r="18">
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>168.3370723102034</v>
+        <v>492.5794965526277</v>
       </c>
       <c r="C18" t="n">
         <v>127.8321102440223</v>
@@ -5624,13 +5624,13 @@
         <v>1364.015253264682</v>
       </c>
       <c r="W18" t="n">
-        <v>927.2747048709159</v>
+        <v>1251.51712911334</v>
       </c>
       <c r="X18" t="n">
-        <v>503.1709276533527</v>
+        <v>1151.655776138201</v>
       </c>
       <c r="Y18" t="n">
-        <v>232.5356143772</v>
+        <v>748.2301268794796</v>
       </c>
     </row>
     <row r="19">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>677.570919560543</v>
+        <v>686.6827231319049</v>
       </c>
       <c r="C19" t="n">
-        <v>725.3629253789787</v>
+        <v>734.4747289503407</v>
       </c>
       <c r="D19" t="n">
-        <v>760.4720695039788</v>
+        <v>769.5838730753408</v>
       </c>
       <c r="E19" t="n">
-        <v>800.0909737153918</v>
+        <v>809.2027772867538</v>
       </c>
       <c r="F19" t="n">
         <v>846.2419463073272</v>
@@ -5709,7 +5709,7 @@
         <v>619.9360847865805</v>
       </c>
       <c r="Y19" t="n">
-        <v>644.0235818942508</v>
+        <v>653.1353854656128</v>
       </c>
     </row>
     <row r="20">
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.4271111840277</v>
+        <v>596.4271111840278</v>
       </c>
       <c r="C20" t="n">
-        <v>466.6548099284783</v>
+        <v>466.6548099284784</v>
       </c>
       <c r="D20" t="n">
         <v>376.4132384740846</v>
       </c>
       <c r="E20" t="n">
-        <v>292.2078954368435</v>
+        <v>292.2078954368436</v>
       </c>
       <c r="F20" t="n">
         <v>207.4708967418821</v>
@@ -5743,25 +5743,25 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>561.1174722838869</v>
+        <v>135.1157830635917</v>
       </c>
       <c r="K20" t="n">
-        <v>737.8015633894146</v>
+        <v>311.7998741691194</v>
       </c>
       <c r="L20" t="n">
-        <v>956.9938018818768</v>
+        <v>530.9921126615817</v>
       </c>
       <c r="M20" t="n">
-        <v>1599.503801881877</v>
+        <v>1173.502112661582</v>
       </c>
       <c r="N20" t="n">
-        <v>1643.469637376511</v>
+        <v>1816.012112661582</v>
       </c>
       <c r="O20" t="n">
-        <v>1807.952580216753</v>
+        <v>1980.495055501823</v>
       </c>
       <c r="P20" t="n">
-        <v>2007.406159168438</v>
+        <v>2179.948634453508</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5788,7 +5788,7 @@
         <v>951.292510818756</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.0526798260222</v>
+        <v>759.0526798260223</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1332.516433297332</v>
+        <v>1020.773969443947</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.559382971295</v>
+        <v>980.2690073777661</v>
       </c>
       <c r="D21" t="n">
-        <v>749.1071739837166</v>
+        <v>953.059222632612</v>
       </c>
       <c r="E21" t="n">
-        <v>402.9737424464312</v>
+        <v>739.7161270778955</v>
       </c>
       <c r="F21" t="n">
-        <v>59.90683099403029</v>
+        <v>720.8916398679189</v>
       </c>
       <c r="G21" t="n">
-        <v>55.87768288317744</v>
+        <v>392.6200675146418</v>
       </c>
       <c r="H21" t="n">
-        <v>51.92</v>
+        <v>388.6623846314643</v>
       </c>
       <c r="I21" t="n">
-        <v>51.92</v>
+        <v>388.6623846314643</v>
       </c>
       <c r="J21" t="n">
-        <v>246.0900193262423</v>
+        <v>582.8324039577067</v>
       </c>
       <c r="K21" t="n">
-        <v>555.2888889111919</v>
+        <v>892.0312735426561</v>
       </c>
       <c r="L21" t="n">
-        <v>988.0022990912977</v>
+        <v>1324.744683722762</v>
       </c>
       <c r="M21" t="n">
-        <v>1262.385790834157</v>
+        <v>1599.128175465621</v>
       </c>
       <c r="N21" t="n">
-        <v>1588.95284421531</v>
+        <v>1925.695228846774</v>
       </c>
       <c r="O21" t="n">
-        <v>2004.814927691482</v>
+        <v>2341.557312322946</v>
       </c>
       <c r="P21" t="n">
-        <v>2259.257615368536</v>
+        <v>2596</v>
       </c>
       <c r="Q21" t="n">
-        <v>2259.257615368536</v>
+        <v>2596</v>
       </c>
       <c r="R21" t="n">
-        <v>2077.776973925881</v>
+        <v>2414.519358557345</v>
       </c>
       <c r="S21" t="n">
-        <v>1944.827012078646</v>
+        <v>2281.569396710111</v>
       </c>
       <c r="T21" t="n">
-        <v>1862.673475647767</v>
+        <v>2199.415860279231</v>
       </c>
       <c r="U21" t="n">
-        <v>1782.71289689248</v>
+        <v>2119.455281523944</v>
       </c>
       <c r="V21" t="n">
-        <v>1688.257677507106</v>
+        <v>2025.00006213857</v>
       </c>
       <c r="W21" t="n">
-        <v>1575.759553355764</v>
+        <v>1912.501937987229</v>
       </c>
       <c r="X21" t="n">
-        <v>1475.898200380625</v>
+        <v>1812.64058501209</v>
       </c>
       <c r="Y21" t="n">
-        <v>1396.714975364328</v>
+        <v>1409.214935753368</v>
       </c>
     </row>
     <row r="22">
@@ -5877,28 +5877,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.6827231319049</v>
+        <v>677.570919560543</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4747289503407</v>
+        <v>725.3629253789787</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5838730753408</v>
+        <v>760.4720695039788</v>
       </c>
       <c r="E22" t="n">
-        <v>809.2027772867538</v>
+        <v>800.0909737153918</v>
       </c>
       <c r="F22" t="n">
-        <v>855.3537498786892</v>
+        <v>846.2419463073272</v>
       </c>
       <c r="G22" t="n">
-        <v>931.1733665852466</v>
+        <v>922.0615630138847</v>
       </c>
       <c r="H22" t="n">
-        <v>1028.019439941366</v>
+        <v>1018.907636370004</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.679156254498</v>
+        <v>1180.567352683136</v>
       </c>
       <c r="J22" t="n">
         <v>1507.490786286407</v>
@@ -5922,31 +5922,31 @@
         <v>819.445771165522</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.7485323517867</v>
+        <v>463.7485323517866</v>
       </c>
       <c r="R22" t="n">
-        <v>82.63285414595433</v>
+        <v>82.63285414595431</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4478053883131</v>
+        <v>164.447805388313</v>
       </c>
       <c r="U22" t="n">
-        <v>332.8229826167636</v>
+        <v>323.7111790454016</v>
       </c>
       <c r="V22" t="n">
-        <v>453.4343755027096</v>
+        <v>444.3225719313476</v>
       </c>
       <c r="W22" t="n">
-        <v>547.115293762387</v>
+        <v>538.003490191025</v>
       </c>
       <c r="X22" t="n">
-        <v>619.9360847865805</v>
+        <v>610.8242812152185</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.1353854656128</v>
+        <v>644.0235818942508</v>
       </c>
     </row>
     <row r="23">
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.4271111840278</v>
+        <v>597.6737579821468</v>
       </c>
       <c r="C23" t="n">
-        <v>466.6548099284784</v>
+        <v>467.9014567265973</v>
       </c>
       <c r="D23" t="n">
-        <v>376.4132384740846</v>
+        <v>377.6598852722036</v>
       </c>
       <c r="E23" t="n">
-        <v>292.2078954368436</v>
+        <v>293.4545422349625</v>
       </c>
       <c r="F23" t="n">
-        <v>207.4708967418821</v>
+        <v>208.717543540001</v>
       </c>
       <c r="G23" t="n">
-        <v>125.2947783462868</v>
+        <v>126.5414251444057</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>53.16664679811893</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
@@ -5983,19 +5983,19 @@
         <v>135.1157830635917</v>
       </c>
       <c r="K23" t="n">
-        <v>777.6257830635917</v>
+        <v>727.8512397156111</v>
       </c>
       <c r="L23" t="n">
-        <v>1420.135783063592</v>
+        <v>947.0434782080733</v>
       </c>
       <c r="M23" t="n">
-        <v>1789.007057159758</v>
+        <v>1589.553478208073</v>
       </c>
       <c r="N23" t="n">
-        <v>1789.007057159758</v>
+        <v>2232.063478208073</v>
       </c>
       <c r="O23" t="n">
-        <v>1953.49</v>
+        <v>2396.546421048315</v>
       </c>
       <c r="P23" t="n">
         <v>2596</v>
@@ -6013,19 +6013,19 @@
         <v>2190.534499991642</v>
       </c>
       <c r="U23" t="n">
-        <v>1857.864564968695</v>
+        <v>1859.111211766814</v>
       </c>
       <c r="V23" t="n">
-        <v>1545.893833487054</v>
+        <v>1547.140480285173</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.31456481943</v>
+        <v>1226.561211617549</v>
       </c>
       <c r="X23" t="n">
-        <v>951.292510818756</v>
+        <v>952.5391576168749</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.0526798260223</v>
+        <v>760.2993266241413</v>
       </c>
     </row>
     <row r="24">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1332.516433297332</v>
+        <v>492.5794965526277</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.559382971295</v>
+        <v>452.0745344864466</v>
       </c>
       <c r="D24" t="n">
-        <v>749.1071739837167</v>
+        <v>424.8647497412924</v>
       </c>
       <c r="E24" t="n">
         <v>402.9737424464312</v>
       </c>
       <c r="F24" t="n">
-        <v>59.9068309940303</v>
+        <v>384.1492552364546</v>
       </c>
       <c r="G24" t="n">
         <v>55.87768288317746</v>
@@ -6092,19 +6092,19 @@
         <v>1862.673475647767</v>
       </c>
       <c r="U24" t="n">
-        <v>1782.71289689248</v>
+        <v>1458.470472650056</v>
       </c>
       <c r="V24" t="n">
-        <v>1688.257677507106</v>
+        <v>1364.015253264682</v>
       </c>
       <c r="W24" t="n">
-        <v>1575.759553355764</v>
+        <v>1060.065040853485</v>
       </c>
       <c r="X24" t="n">
-        <v>1475.898200380625</v>
+        <v>960.2036878783459</v>
       </c>
       <c r="Y24" t="n">
-        <v>1396.714975364328</v>
+        <v>881.0204628620486</v>
       </c>
     </row>
     <row r="25">
@@ -6114,25 +6114,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>677.570919560543</v>
+        <v>686.6827231319049</v>
       </c>
       <c r="C25" t="n">
-        <v>725.3629253789787</v>
+        <v>734.4747289503407</v>
       </c>
       <c r="D25" t="n">
-        <v>760.4720695039788</v>
+        <v>769.5838730753408</v>
       </c>
       <c r="E25" t="n">
-        <v>800.0909737153918</v>
+        <v>809.2027772867538</v>
       </c>
       <c r="F25" t="n">
-        <v>846.2419463073272</v>
+        <v>855.3537498786892</v>
       </c>
       <c r="G25" t="n">
-        <v>922.0615630138847</v>
+        <v>931.1733665852466</v>
       </c>
       <c r="H25" t="n">
-        <v>1018.907636370004</v>
+        <v>1028.019439941366</v>
       </c>
       <c r="I25" t="n">
         <v>1180.567352683136</v>
@@ -6183,7 +6183,7 @@
         <v>619.9360847865805</v>
       </c>
       <c r="Y25" t="n">
-        <v>644.0235818942508</v>
+        <v>653.1353854656128</v>
       </c>
     </row>
     <row r="26">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.5071111840277</v>
+        <v>601.6737579821468</v>
       </c>
       <c r="C26" t="n">
-        <v>466.7348099284783</v>
+        <v>471.9014567265973</v>
       </c>
       <c r="D26" t="n">
-        <v>376.4932384740846</v>
+        <v>381.6598852722036</v>
       </c>
       <c r="E26" t="n">
-        <v>292.2878954368435</v>
+        <v>297.4545422349625</v>
       </c>
       <c r="F26" t="n">
-        <v>207.5508967418821</v>
+        <v>212.717543540001</v>
       </c>
       <c r="G26" t="n">
-        <v>125.3747783462868</v>
+        <v>130.5414251444057</v>
       </c>
       <c r="H26" t="n">
-        <v>52</v>
+        <v>57.16664679811892</v>
       </c>
       <c r="I26" t="n">
         <v>52</v>
@@ -6226,13 +6226,13 @@
         <v>531.0721126615816</v>
       </c>
       <c r="M26" t="n">
-        <v>1174.572112661582</v>
+        <v>669.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1818.072112661582</v>
+        <v>1313</v>
       </c>
       <c r="O26" t="n">
-        <v>1982.555055501823</v>
+        <v>1956.5</v>
       </c>
       <c r="P26" t="n">
         <v>2600</v>
@@ -6241,28 +6241,28 @@
         <v>2600</v>
       </c>
       <c r="R26" t="n">
-        <v>2594.833353201881</v>
+        <v>2600</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.523290805747</v>
+        <v>2456.689937603866</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.367853193523</v>
+        <v>2194.534499991642</v>
       </c>
       <c r="U26" t="n">
-        <v>1857.944564968695</v>
+        <v>1863.111211766814</v>
       </c>
       <c r="V26" t="n">
-        <v>1545.973833487054</v>
+        <v>1551.140480285173</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.39456481943</v>
+        <v>1230.561211617549</v>
       </c>
       <c r="X26" t="n">
-        <v>951.3725108187559</v>
+        <v>956.5391576168749</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.1326798260222</v>
+        <v>764.2993266241413</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>816.901920795052</v>
+        <v>1008.354009054907</v>
       </c>
       <c r="C27" t="n">
-        <v>776.3969587288709</v>
+        <v>645.3672932484338</v>
       </c>
       <c r="D27" t="n">
-        <v>749.1871739837168</v>
+        <v>618.1575085032797</v>
       </c>
       <c r="E27" t="n">
-        <v>403.0537424464312</v>
+        <v>596.2665012084185</v>
       </c>
       <c r="F27" t="n">
-        <v>59.9868309940303</v>
+        <v>253.1995897560176</v>
       </c>
       <c r="G27" t="n">
-        <v>55.95768288317746</v>
+        <v>249.1704416451647</v>
       </c>
       <c r="H27" t="n">
-        <v>52</v>
+        <v>245.2127587619873</v>
       </c>
       <c r="I27" t="n">
         <v>52</v>
@@ -6320,28 +6320,28 @@
         <v>2259.337615368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1886.404885666026</v>
+        <v>2077.856973925881</v>
       </c>
       <c r="S27" t="n">
-        <v>1753.454923818791</v>
+        <v>1944.907012078646</v>
       </c>
       <c r="T27" t="n">
-        <v>1671.301387387912</v>
+        <v>1538.511051405343</v>
       </c>
       <c r="U27" t="n">
-        <v>1591.340808632625</v>
+        <v>1458.550472650056</v>
       </c>
       <c r="V27" t="n">
-        <v>1496.885589247251</v>
+        <v>1364.095253264682</v>
       </c>
       <c r="W27" t="n">
-        <v>1384.387465095909</v>
+        <v>1251.59712911334</v>
       </c>
       <c r="X27" t="n">
-        <v>960.2836878783459</v>
+        <v>1151.735776138201</v>
       </c>
       <c r="Y27" t="n">
-        <v>881.1004628620485</v>
+        <v>1072.552551121904</v>
       </c>
     </row>
     <row r="28">
@@ -6460,19 +6460,19 @@
         <v>311.8798741691194</v>
       </c>
       <c r="L29" t="n">
-        <v>955.3798741691194</v>
+        <v>531.0721126615816</v>
       </c>
       <c r="M29" t="n">
-        <v>1592.563478208073</v>
+        <v>1003.969637376511</v>
       </c>
       <c r="N29" t="n">
-        <v>2236.063478208073</v>
+        <v>1647.469637376511</v>
       </c>
       <c r="O29" t="n">
-        <v>2400.546421048315</v>
+        <v>1811.952580216753</v>
       </c>
       <c r="P29" t="n">
-        <v>2600</v>
+        <v>2011.406159168438</v>
       </c>
       <c r="Q29" t="n">
         <v>2600</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>492.6594965526278</v>
+        <v>1008.354009054907</v>
       </c>
       <c r="C30" t="n">
-        <v>452.1545344864467</v>
+        <v>967.8490469887263</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9447497412925</v>
+        <v>940.6392622435721</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0537424464312</v>
+        <v>594.5058307062866</v>
       </c>
       <c r="F30" t="n">
-        <v>59.98683099403029</v>
+        <v>384.2292552364546</v>
       </c>
       <c r="G30" t="n">
-        <v>55.95768288317743</v>
+        <v>380.2001071256017</v>
       </c>
       <c r="H30" t="n">
         <v>52</v>
@@ -6563,22 +6563,22 @@
         <v>1944.907012078646</v>
       </c>
       <c r="T30" t="n">
-        <v>1862.753475647767</v>
+        <v>1538.511051405343</v>
       </c>
       <c r="U30" t="n">
-        <v>1782.79289689248</v>
+        <v>1458.550472650056</v>
       </c>
       <c r="V30" t="n">
-        <v>1496.885589247251</v>
+        <v>1364.095253264682</v>
       </c>
       <c r="W30" t="n">
-        <v>1060.145040853485</v>
+        <v>1251.59712911334</v>
       </c>
       <c r="X30" t="n">
-        <v>636.0412636359217</v>
+        <v>1151.735776138201</v>
       </c>
       <c r="Y30" t="n">
-        <v>556.8580386196244</v>
+        <v>1072.552551121904</v>
       </c>
     </row>
     <row r="31">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>686.7627231319051</v>
+        <v>677.6509195605429</v>
       </c>
       <c r="C31" t="n">
-        <v>734.5547289503409</v>
+        <v>725.4429253789787</v>
       </c>
       <c r="D31" t="n">
         <v>760.5520695039787</v>
@@ -6651,13 +6651,13 @@
         <v>453.5143755027096</v>
       </c>
       <c r="W31" t="n">
-        <v>547.1952937623871</v>
+        <v>538.0834901910249</v>
       </c>
       <c r="X31" t="n">
-        <v>620.0160847865807</v>
+        <v>610.9042812152185</v>
       </c>
       <c r="Y31" t="n">
-        <v>653.2153854656129</v>
+        <v>644.1035818942507</v>
       </c>
     </row>
     <row r="32">
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.5071111840277</v>
+        <v>601.6737579821468</v>
       </c>
       <c r="C32" t="n">
-        <v>466.7348099284783</v>
+        <v>471.9014567265973</v>
       </c>
       <c r="D32" t="n">
-        <v>376.4932384740846</v>
+        <v>381.6598852722036</v>
       </c>
       <c r="E32" t="n">
-        <v>292.2878954368435</v>
+        <v>297.4545422349625</v>
       </c>
       <c r="F32" t="n">
-        <v>207.5508967418821</v>
+        <v>212.717543540001</v>
       </c>
       <c r="G32" t="n">
-        <v>125.3747783462868</v>
+        <v>130.5414251444058</v>
       </c>
       <c r="H32" t="n">
-        <v>52</v>
+        <v>57.16664679811899</v>
       </c>
       <c r="I32" t="n">
         <v>52</v>
       </c>
       <c r="J32" t="n">
-        <v>135.1957830635917</v>
+        <v>561.1974722838869</v>
       </c>
       <c r="K32" t="n">
-        <v>311.8798741691194</v>
+        <v>1204.697472283887</v>
       </c>
       <c r="L32" t="n">
-        <v>949.0634782080733</v>
+        <v>1423.889710776349</v>
       </c>
       <c r="M32" t="n">
-        <v>1592.563478208073</v>
+        <v>1423.889710776349</v>
       </c>
       <c r="N32" t="n">
-        <v>2236.063478208073</v>
+        <v>1423.889710776349</v>
       </c>
       <c r="O32" t="n">
-        <v>2400.546421048315</v>
+        <v>2067.38971077635</v>
       </c>
       <c r="P32" t="n">
-        <v>2600</v>
+        <v>2266.843289728035</v>
       </c>
       <c r="Q32" t="n">
         <v>2600</v>
@@ -6718,25 +6718,25 @@
         <v>2600</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.523290805747</v>
+        <v>2456.689937603866</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.367853193523</v>
+        <v>2194.534499991642</v>
       </c>
       <c r="U32" t="n">
-        <v>1857.944564968695</v>
+        <v>1863.111211766814</v>
       </c>
       <c r="V32" t="n">
-        <v>1545.973833487054</v>
+        <v>1551.140480285173</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.39456481943</v>
+        <v>1230.561211617549</v>
       </c>
       <c r="X32" t="n">
-        <v>951.3725108187559</v>
+        <v>956.5391576168749</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.1326798260222</v>
+        <v>764.2993266241413</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1008.354009054907</v>
+        <v>684.111584812483</v>
       </c>
       <c r="C33" t="n">
-        <v>776.3969587288709</v>
+        <v>319.3641985038776</v>
       </c>
       <c r="D33" t="n">
-        <v>424.9447497412925</v>
+        <v>292.1544137587234</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0537424464312</v>
+        <v>270.2634064638622</v>
       </c>
       <c r="F33" t="n">
-        <v>59.9868309940303</v>
+        <v>251.4389192538855</v>
       </c>
       <c r="G33" t="n">
-        <v>55.95768288317746</v>
+        <v>247.4097711430327</v>
       </c>
       <c r="H33" t="n">
         <v>52</v>
@@ -6797,13 +6797,13 @@
         <v>2077.856973925881</v>
       </c>
       <c r="S33" t="n">
-        <v>1620.664587836222</v>
+        <v>1944.907012078646</v>
       </c>
       <c r="T33" t="n">
-        <v>1538.511051405343</v>
+        <v>1862.753475647767</v>
       </c>
       <c r="U33" t="n">
-        <v>1458.550472650056</v>
+        <v>1782.79289689248</v>
       </c>
       <c r="V33" t="n">
         <v>1364.095253264682</v>
@@ -6870,10 +6870,10 @@
         <v>819.525771165522</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.8285323517866</v>
+        <v>463.8285323517867</v>
       </c>
       <c r="R34" t="n">
-        <v>82.71285414595431</v>
+        <v>82.71285414595432</v>
       </c>
       <c r="S34" t="n">
         <v>52</v>
@@ -6882,7 +6882,7 @@
         <v>164.5278053883131</v>
       </c>
       <c r="U34" t="n">
-        <v>323.7911790454015</v>
+        <v>332.9029826167637</v>
       </c>
       <c r="V34" t="n">
         <v>444.4025719313475</v>
@@ -6928,25 +6928,25 @@
         <v>45.04</v>
       </c>
       <c r="J35" t="n">
-        <v>128.2357830635917</v>
+        <v>215.9534782080734</v>
       </c>
       <c r="K35" t="n">
-        <v>304.9198741691194</v>
+        <v>773.3234782080734</v>
       </c>
       <c r="L35" t="n">
-        <v>524.1121126615817</v>
+        <v>1330.693478208073</v>
       </c>
       <c r="M35" t="n">
-        <v>1081.482112661582</v>
+        <v>1888.063478208073</v>
       </c>
       <c r="N35" t="n">
-        <v>1638.852112661581</v>
+        <v>1888.063478208073</v>
       </c>
       <c r="O35" t="n">
-        <v>1803.335055501823</v>
+        <v>2052.546421048315</v>
       </c>
       <c r="P35" t="n">
-        <v>2002.788634453508</v>
+        <v>2252</v>
       </c>
       <c r="Q35" t="n">
         <v>2252</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>928.7496756664767</v>
+        <v>846.4709391409167</v>
       </c>
       <c r="C36" t="n">
-        <v>912.4871378427199</v>
+        <v>481.7235528323113</v>
       </c>
       <c r="D36" t="n">
-        <v>909.51977733999</v>
+        <v>478.7561923295814</v>
       </c>
       <c r="E36" t="n">
-        <v>909.51977733999</v>
+        <v>388.1069114524009</v>
       </c>
       <c r="F36" t="n">
-        <v>566.452865887589</v>
+        <v>45.04</v>
       </c>
       <c r="G36" t="n">
-        <v>566.452865887589</v>
+        <v>45.04</v>
       </c>
       <c r="H36" t="n">
-        <v>238.2527587619873</v>
+        <v>45.04</v>
       </c>
       <c r="I36" t="n">
         <v>45.04</v>
@@ -7013,7 +7013,7 @@
         <v>548.4088889111918</v>
       </c>
       <c r="L36" t="n">
-        <v>981.1222990912976</v>
+        <v>980.7446837227624</v>
       </c>
       <c r="M36" t="n">
         <v>1255.128175465622</v>
@@ -7031,28 +7031,28 @@
         <v>2252</v>
       </c>
       <c r="R36" t="n">
-        <v>2094.761782799769</v>
+        <v>1746.276934314921</v>
       </c>
       <c r="S36" t="n">
-        <v>1986.054245194959</v>
+        <v>1637.56939671011</v>
       </c>
       <c r="T36" t="n">
-        <v>1928.143133006504</v>
+        <v>1579.658284521655</v>
       </c>
       <c r="U36" t="n">
-        <v>1872.424978493641</v>
+        <v>1523.940130008793</v>
       </c>
       <c r="V36" t="n">
-        <v>1802.212183350691</v>
+        <v>1453.727334865843</v>
       </c>
       <c r="W36" t="n">
-        <v>1447.750371482485</v>
+        <v>1016.986786472077</v>
       </c>
       <c r="X36" t="n">
-        <v>1023.646594264922</v>
+        <v>941.3678577393621</v>
       </c>
       <c r="Y36" t="n">
-        <v>968.705793491049</v>
+        <v>886.427056965489</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>349.6339351881433</v>
+        <v>653.9875459034544</v>
       </c>
       <c r="C37" t="n">
-        <v>349.6339351881433</v>
+        <v>725.5395517218901</v>
       </c>
       <c r="D37" t="n">
-        <v>408.5030793131433</v>
+        <v>784.4086958468902</v>
       </c>
       <c r="E37" t="n">
-        <v>471.8819835245563</v>
+        <v>847.7876000583032</v>
       </c>
       <c r="F37" t="n">
-        <v>541.7929561164918</v>
+        <v>847.7876000583032</v>
       </c>
       <c r="G37" t="n">
-        <v>641.3725728230493</v>
+        <v>847.7876000583032</v>
       </c>
       <c r="H37" t="n">
-        <v>761.9786461791682</v>
+        <v>847.7876000583032</v>
       </c>
       <c r="I37" t="n">
-        <v>947.3983624923003</v>
+        <v>1033.207316371435</v>
       </c>
       <c r="J37" t="n">
         <v>1298.081796095571</v>
@@ -7122,16 +7122,16 @@
         <v>181.327805388313</v>
       </c>
       <c r="V37" t="n">
-        <v>195.7458064976576</v>
+        <v>325.699198274259</v>
       </c>
       <c r="W37" t="n">
-        <v>195.7458064976576</v>
+        <v>443.1401165339364</v>
       </c>
       <c r="X37" t="n">
-        <v>292.3265975218511</v>
+        <v>539.72090755813</v>
       </c>
       <c r="Y37" t="n">
-        <v>292.3265975218511</v>
+        <v>596.6802082371622</v>
       </c>
     </row>
     <row r="38">
@@ -7171,19 +7171,19 @@
         <v>730.9215633894146</v>
       </c>
       <c r="L38" t="n">
-        <v>950.1138018818768</v>
+        <v>1288.291563389414</v>
       </c>
       <c r="M38" t="n">
-        <v>1507.483801881877</v>
+        <v>1288.291563389414</v>
       </c>
       <c r="N38" t="n">
-        <v>1507.483801881877</v>
+        <v>1288.291563389414</v>
       </c>
       <c r="O38" t="n">
-        <v>1671.966744722118</v>
+        <v>1452.774506229656</v>
       </c>
       <c r="P38" t="n">
-        <v>1871.420323673803</v>
+        <v>2010.144506229656</v>
       </c>
       <c r="Q38" t="n">
         <v>2252</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>407.3368097788878</v>
+        <v>1081.670348441775</v>
       </c>
       <c r="C39" t="n">
-        <v>391.0742719551309</v>
+        <v>1065.407810618018</v>
       </c>
       <c r="D39" t="n">
-        <v>388.1069114524009</v>
+        <v>1062.440450115288</v>
       </c>
       <c r="E39" t="n">
-        <v>388.1069114524009</v>
+        <v>716.3070185780027</v>
       </c>
       <c r="F39" t="n">
-        <v>45.04</v>
+        <v>373.2401071256018</v>
       </c>
       <c r="G39" t="n">
-        <v>45.04</v>
+        <v>373.2401071256018</v>
       </c>
       <c r="H39" t="n">
         <v>45.04</v>
@@ -7250,10 +7250,10 @@
         <v>548.4088889111918</v>
       </c>
       <c r="L39" t="n">
-        <v>980.7446837227624</v>
+        <v>981.1222990912976</v>
       </c>
       <c r="M39" t="n">
-        <v>1255.128175465622</v>
+        <v>1255.505790834157</v>
       </c>
       <c r="N39" t="n">
         <v>1581.695228846775</v>
@@ -7271,25 +7271,25 @@
         <v>2094.761782799769</v>
       </c>
       <c r="S39" t="n">
-        <v>1895.404964317778</v>
+        <v>1872.768806010969</v>
       </c>
       <c r="T39" t="n">
-        <v>1837.493852129323</v>
+        <v>1814.857693822514</v>
       </c>
       <c r="U39" t="n">
-        <v>1433.290849131612</v>
+        <v>1759.139539309651</v>
       </c>
       <c r="V39" t="n">
-        <v>1014.593205503814</v>
+        <v>1688.926744166701</v>
       </c>
       <c r="W39" t="n">
-        <v>577.8526571100479</v>
+        <v>1252.186195772935</v>
       </c>
       <c r="X39" t="n">
-        <v>502.2337283773332</v>
+        <v>1176.56726704022</v>
       </c>
       <c r="Y39" t="n">
-        <v>447.2929276034601</v>
+        <v>1121.626466266348</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>790.1831329688771</v>
+        <v>391.0633059189362</v>
       </c>
       <c r="C40" t="n">
-        <v>861.7351387873128</v>
+        <v>391.0633059189362</v>
       </c>
       <c r="D40" t="n">
-        <v>920.6042829123129</v>
+        <v>449.9324500439363</v>
       </c>
       <c r="E40" t="n">
-        <v>983.9831871237259</v>
+        <v>513.3113542553493</v>
       </c>
       <c r="F40" t="n">
-        <v>1053.894159715661</v>
+        <v>583.2223268472849</v>
       </c>
       <c r="G40" t="n">
-        <v>1153.473776422219</v>
+        <v>626.5040601090866</v>
       </c>
       <c r="H40" t="n">
-        <v>1274.079849778338</v>
+        <v>747.1101334652055</v>
       </c>
       <c r="I40" t="n">
-        <v>1274.079849778338</v>
+        <v>932.5298497783376</v>
       </c>
       <c r="J40" t="n">
         <v>1283.213283381609</v>
@@ -7353,22 +7353,22 @@
         <v>45.04</v>
       </c>
       <c r="T40" t="n">
-        <v>125.3882152252852</v>
+        <v>45.04</v>
       </c>
       <c r="U40" t="n">
-        <v>317.5233924537358</v>
+        <v>237.1751772284506</v>
       </c>
       <c r="V40" t="n">
-        <v>461.8947853396817</v>
+        <v>237.1751772284506</v>
       </c>
       <c r="W40" t="n">
-        <v>579.3357035993591</v>
+        <v>237.1751772284506</v>
       </c>
       <c r="X40" t="n">
-        <v>675.9164946235527</v>
+        <v>333.7559682526441</v>
       </c>
       <c r="Y40" t="n">
-        <v>732.8757953025849</v>
+        <v>333.7559682526441</v>
       </c>
     </row>
     <row r="41">
@@ -7402,25 +7402,25 @@
         <v>45.04</v>
       </c>
       <c r="J41" t="n">
-        <v>554.2374722838869</v>
+        <v>128.2357830635917</v>
       </c>
       <c r="K41" t="n">
-        <v>730.9215633894146</v>
+        <v>304.9198741691194</v>
       </c>
       <c r="L41" t="n">
-        <v>950.1138018818768</v>
+        <v>773.3234782080734</v>
       </c>
       <c r="M41" t="n">
-        <v>950.113801881877</v>
+        <v>1330.693478208073</v>
       </c>
       <c r="N41" t="n">
-        <v>1330.693478208073</v>
+        <v>1888.063478208073</v>
       </c>
       <c r="O41" t="n">
-        <v>1495.176421048315</v>
+        <v>2052.546421048315</v>
       </c>
       <c r="P41" t="n">
-        <v>1694.63</v>
+        <v>2252</v>
       </c>
       <c r="Q41" t="n">
         <v>2252</v>
@@ -7432,19 +7432,19 @@
         <v>2108.689937603866</v>
       </c>
       <c r="T41" t="n">
-        <v>2108.689937603866</v>
+        <v>1846.534499991642</v>
       </c>
       <c r="U41" t="n">
-        <v>1777.266649379038</v>
+        <v>1515.111211766814</v>
       </c>
       <c r="V41" t="n">
-        <v>1465.295917897397</v>
+        <v>1203.140480285173</v>
       </c>
       <c r="W41" t="n">
-        <v>1144.716649229773</v>
+        <v>882.5612116175494</v>
       </c>
       <c r="X41" t="n">
-        <v>944.4125108187559</v>
+        <v>882.5612116175494</v>
       </c>
       <c r="Y41" t="n">
         <v>752.1726798260222</v>
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>354.6698310721907</v>
+        <v>485.6994965526277</v>
       </c>
       <c r="C42" t="n">
-        <v>314.1648690060096</v>
+        <v>445.1945344864466</v>
       </c>
       <c r="D42" t="n">
-        <v>286.9550842608554</v>
+        <v>417.9847497412924</v>
       </c>
       <c r="E42" t="n">
-        <v>265.0640769659942</v>
+        <v>396.0937424464312</v>
       </c>
       <c r="F42" t="n">
-        <v>246.2395897560175</v>
+        <v>53.02683099403028</v>
       </c>
       <c r="G42" t="n">
-        <v>242.2104416451647</v>
+        <v>48.99768288317743</v>
       </c>
       <c r="H42" t="n">
-        <v>238.2527587619873</v>
+        <v>45.04</v>
       </c>
       <c r="I42" t="n">
         <v>45.04</v>
@@ -7487,46 +7487,46 @@
         <v>548.4088889111918</v>
       </c>
       <c r="L42" t="n">
-        <v>980.7446837228138</v>
+        <v>980.744683722821</v>
       </c>
       <c r="M42" t="n">
-        <v>1255.128175465673</v>
+        <v>1255.12817546568</v>
       </c>
       <c r="N42" t="n">
-        <v>1581.695228846826</v>
+        <v>1581.695228846833</v>
       </c>
       <c r="O42" t="n">
-        <v>1997.557312322998</v>
+        <v>1997.557312323005</v>
       </c>
       <c r="P42" t="n">
-        <v>2252.000000000051</v>
+        <v>2252.000000000059</v>
       </c>
       <c r="Q42" t="n">
-        <v>2173.963921292306</v>
+        <v>2252.000000000059</v>
       </c>
       <c r="R42" t="n">
-        <v>1668.240855607226</v>
+        <v>1879.444885666026</v>
       </c>
       <c r="S42" t="n">
-        <v>1535.290893759992</v>
+        <v>1422.252499576367</v>
       </c>
       <c r="T42" t="n">
-        <v>1453.137357329113</v>
+        <v>1340.098963145488</v>
       </c>
       <c r="U42" t="n">
-        <v>1048.934354331401</v>
+        <v>1260.138384390201</v>
       </c>
       <c r="V42" t="n">
-        <v>710.4110752819655</v>
+        <v>1165.683165004827</v>
       </c>
       <c r="W42" t="n">
-        <v>597.9129511306236</v>
+        <v>1053.185040853485</v>
       </c>
       <c r="X42" t="n">
-        <v>498.0515981554847</v>
+        <v>953.3236878783459</v>
       </c>
       <c r="Y42" t="n">
-        <v>418.8683731391873</v>
+        <v>549.8980386196243</v>
       </c>
     </row>
     <row r="43">
@@ -7539,25 +7539,25 @@
         <v>679.8027231319051</v>
       </c>
       <c r="C43" t="n">
-        <v>727.5947289503408</v>
+        <v>718.4829253789786</v>
       </c>
       <c r="D43" t="n">
-        <v>762.7038730753409</v>
+        <v>753.5920695039787</v>
       </c>
       <c r="E43" t="n">
-        <v>802.3227772867539</v>
+        <v>793.2109737153917</v>
       </c>
       <c r="F43" t="n">
-        <v>848.4737498786893</v>
+        <v>839.3619463073271</v>
       </c>
       <c r="G43" t="n">
-        <v>924.2933665852468</v>
+        <v>915.1815630138846</v>
       </c>
       <c r="H43" t="n">
-        <v>1021.139439941366</v>
+        <v>1012.027636370003</v>
       </c>
       <c r="I43" t="n">
-        <v>1182.799156254498</v>
+        <v>1173.687352683135</v>
       </c>
       <c r="J43" t="n">
         <v>1500.610786286406</v>
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>589.5471111840278</v>
+        <v>527.6958119828212</v>
       </c>
       <c r="C44" t="n">
-        <v>459.7748099284784</v>
+        <v>397.9235107272717</v>
       </c>
       <c r="D44" t="n">
         <v>369.5332384740846</v>
@@ -7639,16 +7639,16 @@
         <v>45.04</v>
       </c>
       <c r="J44" t="n">
-        <v>128.2357830635917</v>
+        <v>554.2374722838869</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9198741691194</v>
+        <v>773.3234782080734</v>
       </c>
       <c r="L44" t="n">
-        <v>524.1121126615817</v>
+        <v>1330.693478208073</v>
       </c>
       <c r="M44" t="n">
-        <v>1081.482112661582</v>
+        <v>1330.693478208073</v>
       </c>
       <c r="N44" t="n">
         <v>1330.693478208073</v>
@@ -7681,10 +7681,10 @@
         <v>882.5612116175494</v>
       </c>
       <c r="X44" t="n">
-        <v>608.5391576168749</v>
+        <v>882.5612116175494</v>
       </c>
       <c r="Y44" t="n">
-        <v>608.5391576168749</v>
+        <v>690.3213806248157</v>
       </c>
     </row>
     <row r="45">
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>485.6994965526277</v>
+        <v>1325.258817928862</v>
       </c>
       <c r="C45" t="n">
-        <v>445.1945344864466</v>
+        <v>960.5114316202562</v>
       </c>
       <c r="D45" t="n">
-        <v>417.9847497412924</v>
+        <v>742.2271739837167</v>
       </c>
       <c r="E45" t="n">
-        <v>71.85131820400693</v>
+        <v>396.0937424464312</v>
       </c>
       <c r="F45" t="n">
-        <v>53.02683099403029</v>
+        <v>377.2692552364546</v>
       </c>
       <c r="G45" t="n">
         <v>48.99768288317746</v>
@@ -7724,46 +7724,46 @@
         <v>548.4088889111918</v>
       </c>
       <c r="L45" t="n">
-        <v>981.1222990912976</v>
+        <v>980.7446837228283</v>
       </c>
       <c r="M45" t="n">
-        <v>1255.128175465673</v>
+        <v>1255.128175465687</v>
       </c>
       <c r="N45" t="n">
-        <v>1581.695228846826</v>
+        <v>1581.695228846841</v>
       </c>
       <c r="O45" t="n">
-        <v>1997.557312322998</v>
+        <v>1997.557312323012</v>
       </c>
       <c r="P45" t="n">
-        <v>2252.000000000051</v>
+        <v>2252.000000000066</v>
       </c>
       <c r="Q45" t="n">
-        <v>2252.000000000051</v>
+        <v>2252.000000000066</v>
       </c>
       <c r="R45" t="n">
-        <v>1879.444885666026</v>
+        <v>2070.519358557411</v>
       </c>
       <c r="S45" t="n">
-        <v>1422.252499576367</v>
+        <v>1937.569396710177</v>
       </c>
       <c r="T45" t="n">
-        <v>1340.098963145487</v>
+        <v>1855.415860279297</v>
       </c>
       <c r="U45" t="n">
-        <v>935.8959601477765</v>
+        <v>1775.45528152401</v>
       </c>
       <c r="V45" t="n">
-        <v>841.4407407624026</v>
+        <v>1681.000062138636</v>
       </c>
       <c r="W45" t="n">
-        <v>728.9426166110607</v>
+        <v>1568.501937987294</v>
       </c>
       <c r="X45" t="n">
-        <v>629.0812636359217</v>
+        <v>1468.640585012155</v>
       </c>
       <c r="Y45" t="n">
-        <v>549.8980386196243</v>
+        <v>1389.457359995858</v>
       </c>
     </row>
     <row r="46">
@@ -7964,16 +7964,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>373.8993027275024</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M2" t="n">
-        <v>845.554996989051</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
         <v>777.3653500296342</v>
@@ -7982,10 +7982,10 @@
         <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>246.8601159786808</v>
       </c>
       <c r="Q2" t="n">
-        <v>309.7251508449954</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>373.5581017224773</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>320.8173266331659</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>470.8491025166892</v>
+        <v>844.8491025166892</v>
       </c>
       <c r="N5" t="n">
-        <v>402.6480334467196</v>
+        <v>635.2823454053</v>
       </c>
       <c r="O5" t="n">
         <v>373.8043318856502</v>
       </c>
       <c r="P5" t="n">
-        <v>314.1651303924402</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>367.4020254776808</v>
+        <v>127.6736190008522</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,25 +8441,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>320.8173266331659</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>308.0221909547739</v>
+        <v>308.0221909547738</v>
       </c>
       <c r="M8" t="n">
-        <v>470.8491025166892</v>
+        <v>844.8491025166892</v>
       </c>
       <c r="N8" t="n">
-        <v>760.8993559437359</v>
+        <v>402.6480334467196</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>245.2337795226225</v>
       </c>
       <c r="P8" t="n">
-        <v>314.1651303924402</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>127.6736190008522</v>
+        <v>501.6736190008522</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8526,7 +8526,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M9" t="n">
-        <v>471.6948204301074</v>
+        <v>468.8522544012835</v>
       </c>
       <c r="N9" t="n">
         <v>485.4085271713503</v>
@@ -8535,7 +8535,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
-        <v>216.3081458117257</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>317.3353317615616</v>
       </c>
       <c r="K11" t="n">
         <v>470.5312211055276</v>
       </c>
       <c r="L11" t="n">
-        <v>427.5936984924624</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>946.904956788046</v>
+        <v>297.904956788046</v>
       </c>
       <c r="N11" t="n">
-        <v>398.0344556270751</v>
+        <v>226.9054706326493</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>482.8556132926853</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>447.5317384326413</v>
       </c>
       <c r="Q11" t="n">
         <v>21.31284010637989</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>470.5312211055276</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>317.3353317615616</v>
       </c>
       <c r="M14" t="n">
-        <v>543.7831531984698</v>
+        <v>297.904956788046</v>
       </c>
       <c r="N14" t="n">
         <v>226.9054706326493</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>482.8556132926853</v>
       </c>
       <c r="P14" t="n">
         <v>447.5317384326413</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>21.31284010637989</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>191.4174295736177</v>
       </c>
       <c r="L17" t="n">
-        <v>427.5936984924623</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>939.5651628879996</v>
+        <v>946.9049567880461</v>
       </c>
       <c r="N17" t="n">
-        <v>875.9054706326493</v>
+        <v>226.9054706326493</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>447.5317384326413</v>
       </c>
       <c r="Q17" t="n">
         <v>21.31284010637989</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9398,7 +9398,7 @@
         <v>946.9049567880461</v>
       </c>
       <c r="N20" t="n">
-        <v>271.3154054757146</v>
+        <v>875.9054706326493</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>441.5667446987956</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,22 +9626,22 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>470.5312211055276</v>
+        <v>420.2539045924159</v>
       </c>
       <c r="L23" t="n">
-        <v>427.5936984924624</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>670.5022033498306</v>
+        <v>946.9049567880461</v>
       </c>
       <c r="N23" t="n">
-        <v>226.9054706326493</v>
+        <v>875.9054706326493</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>447.5317384326413</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>21.31284010637989</v>
@@ -9869,16 +9869,16 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>947.904956788046</v>
+        <v>437.7311056147311</v>
       </c>
       <c r="N26" t="n">
         <v>876.9054706326493</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>483.8556132926853</v>
       </c>
       <c r="P26" t="n">
-        <v>422.2135005520119</v>
+        <v>448.5317384326413</v>
       </c>
       <c r="Q26" t="n">
         <v>21.31284010637989</v>
@@ -10103,10 +10103,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>428.5936984924623</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>941.5247588475954</v>
+        <v>775.5792241768638</v>
       </c>
       <c r="N29" t="n">
         <v>876.9054706326493</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.31284010637989</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>471.5312211055276</v>
       </c>
       <c r="L32" t="n">
-        <v>422.2135005520117</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>947.9049567880461</v>
+        <v>297.904956788046</v>
       </c>
       <c r="N32" t="n">
-        <v>876.9054706326493</v>
+        <v>226.9054706326493</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>483.8556132926853</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>21.31284010637989</v>
+        <v>357.8347696740213</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>88.60373246917348</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>384.5312211055276</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>341.5936984924623</v>
       </c>
       <c r="M35" t="n">
         <v>860.9049567880461</v>
       </c>
       <c r="N35" t="n">
-        <v>789.9054706326493</v>
+        <v>226.9054706326493</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>273.0414921735436</v>
+        <v>21.31284010637989</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10656,10 +10656,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>388.0893364597981</v>
+        <v>387.7079067946111</v>
       </c>
       <c r="M36" t="n">
-        <v>471.3133907649203</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
         <v>485.4085271713503</v>
@@ -10814,10 +10814,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>341.5936984924622</v>
       </c>
       <c r="M38" t="n">
-        <v>860.9049567880461</v>
+        <v>297.904956788046</v>
       </c>
       <c r="N38" t="n">
         <v>226.9054706326493</v>
@@ -10826,10 +10826,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>361.5317384326413</v>
       </c>
       <c r="Q38" t="n">
-        <v>405.7367555873867</v>
+        <v>265.6113186622832</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,13 +10893,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>387.7079067946111</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>485.4085271713503</v>
+        <v>485.0270975061629</v>
       </c>
       <c r="O39" t="n">
         <v>382.6817988009037</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>251.7286520671634</v>
       </c>
       <c r="M41" t="n">
-        <v>297.904956788046</v>
+        <v>860.9049567880461</v>
       </c>
       <c r="N41" t="n">
-        <v>611.3293861136559</v>
+        <v>789.9054706326493</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>584.3128401063799</v>
+        <v>21.31284010637989</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11130,7 +11130,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>387.707906794663</v>
+        <v>387.7079067946704</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>42.83021698854429</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>341.5936984924623</v>
       </c>
       <c r="M44" t="n">
-        <v>860.9049567880461</v>
+        <v>297.904956788046</v>
       </c>
       <c r="N44" t="n">
-        <v>478.6341226998128</v>
+        <v>226.9054706326493</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11367,10 +11367,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>387.7079067946777</v>
       </c>
       <c r="M45" t="n">
-        <v>471.3133907649722</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
         <v>485.4085271713503</v>
@@ -22527,10 +22527,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.06237890435624e-12</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>8.065284814821125e-13</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -25647,7 +25647,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>259.5338832361016</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -25659,10 +25659,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>72.98073643376046</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>61.2327862091945</v>
       </c>
     </row>
     <row r="42">
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>142.1971869870558</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>61.23278620919455</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -25896,10 +25896,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>190.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357539</v>
       </c>
       <c r="C2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357539</v>
       </c>
       <c r="D2" t="n">
         <v>1353830.31835754</v>
@@ -26296,7 +26296,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="K2" t="n">
-        <v>1353830.318357539</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="L2" t="n">
         <v>1353830.31835754</v>
@@ -26308,7 +26308,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="O2" t="n">
-        <v>1325377.04235239</v>
+        <v>1325377.042352389</v>
       </c>
       <c r="P2" t="n">
         <v>1325377.04235239</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>599936.661423816</v>
+        <v>599737.8665118433</v>
       </c>
       <c r="D4" t="n">
-        <v>597925.8599779638</v>
+        <v>597727.0650659911</v>
       </c>
       <c r="E4" t="n">
-        <v>513503.9011844641</v>
+        <v>513306.8786915817</v>
       </c>
       <c r="F4" t="n">
-        <v>511820.5947772248</v>
+        <v>511623.5722843424</v>
       </c>
       <c r="G4" t="n">
-        <v>510134.9654702991</v>
+        <v>509937.9429774167</v>
       </c>
       <c r="H4" t="n">
-        <v>508446.9966060842</v>
+        <v>508249.9741132018</v>
       </c>
       <c r="I4" t="n">
-        <v>506756.6713099375</v>
+        <v>506559.6488170551</v>
       </c>
       <c r="J4" t="n">
-        <v>504990.7018859815</v>
+        <v>504793.4873038072</v>
       </c>
       <c r="K4" t="n">
-        <v>503296.329942291</v>
+        <v>503099.1153601167</v>
       </c>
       <c r="L4" t="n">
-        <v>501599.5506185964</v>
+        <v>501402.3360364222</v>
       </c>
       <c r="M4" t="n">
-        <v>506037.2264392203</v>
+        <v>505856.7334818643</v>
       </c>
       <c r="N4" t="n">
-        <v>504273.0324747441</v>
+        <v>504092.5395173882</v>
       </c>
       <c r="O4" t="n">
-        <v>488192.3996707719</v>
+        <v>488011.9067134159</v>
       </c>
       <c r="P4" t="n">
-        <v>486484.8207461905</v>
+        <v>486304.3277888344</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>460978.2609954762</v>
+        <v>461177.3525060845</v>
       </c>
       <c r="C6" t="n">
-        <v>694284.6569337238</v>
+        <v>694483.4518456958</v>
       </c>
       <c r="D6" t="n">
-        <v>697270.4583795757</v>
+        <v>697469.2532915487</v>
       </c>
       <c r="E6" t="n">
-        <v>173797.8681730762</v>
+        <v>173994.8906659582</v>
       </c>
       <c r="F6" t="n">
-        <v>767956.1745803152</v>
+        <v>768153.1970731971</v>
       </c>
       <c r="G6" t="n">
-        <v>769641.8038872412</v>
+        <v>769838.8263801232</v>
       </c>
       <c r="H6" t="n">
-        <v>771329.7727514554</v>
+        <v>771526.795244338</v>
       </c>
       <c r="I6" t="n">
-        <v>773020.0980476023</v>
+        <v>773217.1205404847</v>
       </c>
       <c r="J6" t="n">
-        <v>385925.2674715586</v>
+        <v>386122.4820537329</v>
       </c>
       <c r="K6" t="n">
-        <v>776419.6394152483</v>
+        <v>776616.8539974231</v>
       </c>
       <c r="L6" t="n">
-        <v>778116.4187389436</v>
+        <v>778313.6333211174</v>
       </c>
       <c r="M6" t="n">
-        <v>691574.6869183192</v>
+        <v>691755.1798756752</v>
       </c>
       <c r="N6" t="n">
-        <v>778714.8808827957</v>
+        <v>778895.3738401516</v>
       </c>
       <c r="O6" t="n">
-        <v>530759.8936816179</v>
+        <v>530940.3866389734</v>
       </c>
       <c r="P6" t="n">
-        <v>770067.4726061996</v>
+        <v>770247.9655635555</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27036,7 +27036,7 @@
         <v>245</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>224.8682520946261</v>
+        <v>222.9148456338336</v>
       </c>
       <c r="S2" t="n">
-        <v>398.0465935392076</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27515,13 +27515,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>103.2279023104542</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27533,7 +27533,7 @@
         <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27566,13 +27566,13 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>30.46477465147608</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>26.19578428848864</v>
       </c>
       <c r="V3" t="n">
-        <v>104.2915254925638</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27609,16 +27609,16 @@
         <v>244.858135136612</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>365.0353657874031</v>
       </c>
       <c r="I4" t="n">
-        <v>242.0753464069413</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J4" t="n">
         <v>396.1372930982029</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9482601269169</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W4" t="n">
         <v>400</v>
-      </c>
-      <c r="W4" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27682,10 +27682,10 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
+        <v>397.8918749462438</v>
+      </c>
+      <c r="G5" t="n">
         <v>400</v>
-      </c>
-      <c r="G5" t="n">
-        <v>397.8918749462438</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
@@ -27755,10 +27755,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>172.1110334721758</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27767,10 +27767,10 @@
         <v>325.5158377618198</v>
       </c>
       <c r="H6" t="n">
-        <v>243.0776774248062</v>
+        <v>330.0076343562325</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4244990988957</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,19 +27794,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.5243971659513</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
+        <v>88.40890562498866</v>
+      </c>
+      <c r="T6" t="n">
         <v>400</v>
       </c>
-      <c r="T6" t="n">
-        <v>30.45610484015532</v>
-      </c>
       <c r="U6" t="n">
-        <v>26.19564277905465</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,34 +27828,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D7" t="n">
         <v>400</v>
       </c>
-      <c r="D7" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E7" t="n">
-        <v>326.3617730122492</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8563318579235</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.103716265553</v>
+        <v>271.0642752152211</v>
       </c>
       <c r="I7" t="n">
-        <v>170.9935867676593</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.0098012949242</v>
+        <v>22.00980129492416</v>
       </c>
       <c r="K7" t="n">
-        <v>266.7319213421267</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>359.105151834003</v>
+      </c>
+      <c r="T7" t="n">
         <v>400</v>
       </c>
-      <c r="T7" t="n">
-        <v>209.2232550308479</v>
-      </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9481617662612</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53.8914475784365</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.5243971659513</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,13 +28043,13 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>292.4996639586275</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28083,19 +28083,19 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.103716265553</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>170.9935867676593</v>
       </c>
       <c r="J10" t="n">
-        <v>35.30893531714511</v>
+        <v>22.00980129492416</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.7319213421267</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.6653986495825</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,16 +28116,16 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.105151834003</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>209.2232550308479</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9481617662612</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>349.1419351508584</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28162,10 +28162,10 @@
         <v>321</v>
       </c>
       <c r="H11" t="n">
-        <v>319.7658196698623</v>
+        <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>95.99142098921726</v>
+        <v>94.75724065907951</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28226,13 +28226,13 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>131.4624326227433</v>
       </c>
       <c r="D12" t="n">
         <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
         <v>321</v>
@@ -28277,22 +28277,22 @@
         <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>131.4624326227433</v>
+        <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28323,13 +28323,13 @@
         <v>321</v>
       </c>
       <c r="I13" t="n">
+        <v>321</v>
+      </c>
+      <c r="J13" t="n">
+        <v>321</v>
+      </c>
+      <c r="K13" t="n">
         <v>311.7961580087252</v>
-      </c>
-      <c r="J13" t="n">
-        <v>321</v>
-      </c>
-      <c r="K13" t="n">
-        <v>321</v>
       </c>
       <c r="L13" t="n">
         <v>321</v>
@@ -28396,10 +28396,10 @@
         <v>321</v>
       </c>
       <c r="G14" t="n">
-        <v>321</v>
+        <v>319.7658196698623</v>
       </c>
       <c r="H14" t="n">
-        <v>319.7658196698623</v>
+        <v>321</v>
       </c>
       <c r="I14" t="n">
         <v>95.99142098921726</v>
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>131.4624326227433</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28517,7 +28517,7 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>321</v>
@@ -28526,10 +28526,10 @@
         <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>131.4624326227433</v>
       </c>
     </row>
     <row r="16">
@@ -28554,7 +28554,7 @@
         <v>321</v>
       </c>
       <c r="G16" t="n">
-        <v>311.7961580087253</v>
+        <v>321</v>
       </c>
       <c r="H16" t="n">
         <v>321</v>
@@ -28596,7 +28596,7 @@
         <v>321</v>
       </c>
       <c r="U16" t="n">
-        <v>321</v>
+        <v>311.7961580087252</v>
       </c>
       <c r="V16" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>94.75724065907951</v>
+        <v>95.99142098921726</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28675,7 +28675,7 @@
         <v>321</v>
       </c>
       <c r="U17" t="n">
-        <v>321</v>
+        <v>319.7658196698622</v>
       </c>
       <c r="V17" t="n">
         <v>321</v>
@@ -28697,10 +28697,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>131.4624326227432</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>321</v>
@@ -28760,13 +28760,13 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>131.4624326227432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28788,7 +28788,7 @@
         <v>321</v>
       </c>
       <c r="F19" t="n">
-        <v>321</v>
+        <v>311.7961580087252</v>
       </c>
       <c r="G19" t="n">
         <v>321</v>
@@ -28845,7 +28845,7 @@
         <v>321</v>
       </c>
       <c r="Y19" t="n">
-        <v>311.7961580087253</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20">
@@ -28934,22 +28934,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>131.4624326227431</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>131.4624326227433</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>321</v>
@@ -29003,7 +29003,7 @@
         <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>311.7961580087251</v>
+        <v>321</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29070,7 +29070,7 @@
         <v>321</v>
       </c>
       <c r="U22" t="n">
-        <v>321</v>
+        <v>311.7961580087252</v>
       </c>
       <c r="V22" t="n">
         <v>321</v>
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>95.99142098921726</v>
+        <v>94.75724065907951</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29149,7 +29149,7 @@
         <v>321</v>
       </c>
       <c r="U23" t="n">
-        <v>319.7658196698622</v>
+        <v>321</v>
       </c>
       <c r="V23" t="n">
         <v>321</v>
@@ -29171,22 +29171,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>131.4624326227433</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>321</v>
@@ -29228,13 +29228,13 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>131.4624326227432</v>
       </c>
       <c r="X24" t="n">
         <v>321</v>
@@ -29271,7 +29271,7 @@
         <v>321</v>
       </c>
       <c r="I25" t="n">
-        <v>321</v>
+        <v>311.7961580087252</v>
       </c>
       <c r="J25" t="n">
         <v>321</v>
@@ -29319,7 +29319,7 @@
         <v>321</v>
       </c>
       <c r="Y25" t="n">
-        <v>311.7961580087253</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26">
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>95.99142098921726</v>
+        <v>90.87644065907952</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>157.6314727695134</v>
+        <v>162.7464530996513</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29411,13 +29411,13 @@
         <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>1.743063797110494</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -29429,7 +29429,7 @@
         <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>191.2806311743674</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29456,13 +29456,13 @@
         <v>77.25571792066825</v>
       </c>
       <c r="R27" t="n">
-        <v>131.4624326227435</v>
+        <v>321</v>
       </c>
       <c r="S27" t="n">
         <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>321</v>
@@ -29474,7 +29474,7 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29654,16 +29654,16 @@
         <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>131.4624326227432</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>191.2806311743674</v>
@@ -29699,19 +29699,19 @@
         <v>321</v>
       </c>
       <c r="T30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>131.4624326227433</v>
+        <v>321</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29730,64 +29730,64 @@
         <v>321</v>
       </c>
       <c r="D31" t="n">
+        <v>321</v>
+      </c>
+      <c r="E31" t="n">
+        <v>321</v>
+      </c>
+      <c r="F31" t="n">
+        <v>321</v>
+      </c>
+      <c r="G31" t="n">
+        <v>321</v>
+      </c>
+      <c r="H31" t="n">
+        <v>321</v>
+      </c>
+      <c r="I31" t="n">
+        <v>321</v>
+      </c>
+      <c r="J31" t="n">
+        <v>321</v>
+      </c>
+      <c r="K31" t="n">
+        <v>321</v>
+      </c>
+      <c r="L31" t="n">
+        <v>321</v>
+      </c>
+      <c r="M31" t="n">
+        <v>321</v>
+      </c>
+      <c r="N31" t="n">
+        <v>321</v>
+      </c>
+      <c r="O31" t="n">
+        <v>321</v>
+      </c>
+      <c r="P31" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>321</v>
+      </c>
+      <c r="R31" t="n">
+        <v>321</v>
+      </c>
+      <c r="S31" t="n">
+        <v>321</v>
+      </c>
+      <c r="T31" t="n">
+        <v>321</v>
+      </c>
+      <c r="U31" t="n">
+        <v>321</v>
+      </c>
+      <c r="V31" t="n">
+        <v>321</v>
+      </c>
+      <c r="W31" t="n">
         <v>311.7961580087251</v>
-      </c>
-      <c r="E31" t="n">
-        <v>321</v>
-      </c>
-      <c r="F31" t="n">
-        <v>321</v>
-      </c>
-      <c r="G31" t="n">
-        <v>321</v>
-      </c>
-      <c r="H31" t="n">
-        <v>321</v>
-      </c>
-      <c r="I31" t="n">
-        <v>321</v>
-      </c>
-      <c r="J31" t="n">
-        <v>321</v>
-      </c>
-      <c r="K31" t="n">
-        <v>321</v>
-      </c>
-      <c r="L31" t="n">
-        <v>321</v>
-      </c>
-      <c r="M31" t="n">
-        <v>321</v>
-      </c>
-      <c r="N31" t="n">
-        <v>321</v>
-      </c>
-      <c r="O31" t="n">
-        <v>321</v>
-      </c>
-      <c r="P31" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>321</v>
-      </c>
-      <c r="R31" t="n">
-        <v>321</v>
-      </c>
-      <c r="S31" t="n">
-        <v>321</v>
-      </c>
-      <c r="T31" t="n">
-        <v>321</v>
-      </c>
-      <c r="U31" t="n">
-        <v>321</v>
-      </c>
-      <c r="V31" t="n">
-        <v>321</v>
-      </c>
-      <c r="W31" t="n">
-        <v>321</v>
       </c>
       <c r="X31" t="n">
         <v>321</v>
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>95.99142098921726</v>
+        <v>90.87644065907946</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29854,7 +29854,7 @@
         <v>162.7464530996513</v>
       </c>
       <c r="S32" t="n">
-        <v>315.885019669862</v>
+        <v>321</v>
       </c>
       <c r="T32" t="n">
         <v>321</v>
@@ -29882,25 +29882,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>131.4624326227432</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
         <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>321</v>
+        <v>131.4624326227433</v>
       </c>
       <c r="I33" t="n">
         <v>191.2806311743674</v>
@@ -29933,7 +29933,7 @@
         <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T33" t="n">
         <v>321</v>
@@ -29942,7 +29942,7 @@
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>321</v>
@@ -30018,10 +30018,10 @@
         <v>321</v>
       </c>
       <c r="U34" t="n">
+        <v>321</v>
+      </c>
+      <c r="V34" t="n">
         <v>311.7961580087251</v>
-      </c>
-      <c r="V34" t="n">
-        <v>321</v>
       </c>
       <c r="W34" t="n">
         <v>321</v>
@@ -30122,13 +30122,13 @@
         <v>345</v>
       </c>
       <c r="C36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>345</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>252.929309153504</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -30137,10 +30137,10 @@
         <v>324.9888566297443</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>324.9181060543457</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.2806311743674</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30167,7 +30167,7 @@
         <v>77.25571792066825</v>
       </c>
       <c r="R36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>345</v>
@@ -30182,10 +30182,10 @@
         <v>345</v>
       </c>
       <c r="W36" t="n">
-        <v>81.45594916030433</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y36" t="n">
         <v>345</v>
@@ -30201,7 +30201,7 @@
         <v>345</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D37" t="n">
         <v>345</v>
@@ -30210,19 +30210,19 @@
         <v>345</v>
       </c>
       <c r="F37" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>345</v>
+        <v>244.4145285792349</v>
       </c>
       <c r="H37" t="n">
-        <v>345</v>
+        <v>223.1756834786678</v>
       </c>
       <c r="I37" t="n">
         <v>345</v>
       </c>
       <c r="J37" t="n">
-        <v>345</v>
+        <v>258.3242890109747</v>
       </c>
       <c r="K37" t="n">
         <v>345</v>
@@ -30258,16 +30258,16 @@
         <v>150.9240634056055</v>
       </c>
       <c r="V37" t="n">
-        <v>213.7339477004026</v>
+        <v>345</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X37" t="n">
         <v>345</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30365,7 +30365,7 @@
         <v>345</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -30374,7 +30374,7 @@
         <v>324.9888566297443</v>
       </c>
       <c r="H39" t="n">
-        <v>324.9181060543457</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>191.2806311743674</v>
@@ -30407,16 +30407,16 @@
         <v>345</v>
       </c>
       <c r="S39" t="n">
-        <v>255.2572119315913</v>
+        <v>232.8474152078498</v>
       </c>
       <c r="T39" t="n">
         <v>345</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -30438,7 +30438,7 @@
         <v>345</v>
       </c>
       <c r="C40" t="n">
-        <v>345</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
         <v>345</v>
@@ -30450,16 +30450,16 @@
         <v>345</v>
       </c>
       <c r="G40" t="n">
-        <v>345</v>
+        <v>288.1334510659033</v>
       </c>
       <c r="H40" t="n">
         <v>345</v>
       </c>
       <c r="I40" t="n">
-        <v>157.7073572594625</v>
+        <v>345</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="K40" t="n">
         <v>345</v>
@@ -30489,22 +30489,22 @@
         <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>288.4953634716891</v>
+        <v>207.3355501128151</v>
       </c>
       <c r="U40" t="n">
         <v>345</v>
       </c>
       <c r="V40" t="n">
-        <v>345</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>345</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>345</v>
       </c>
       <c r="Y40" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30605,7 +30605,7 @@
         <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30614,7 +30614,7 @@
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.2806311743674</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,22 +30638,22 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>77.25571792066825</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>131.8362718375358</v>
       </c>
       <c r="S42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>79.37262093257857</v>
+        <v>321</v>
       </c>
       <c r="W42" t="n">
         <v>321</v>
@@ -30662,7 +30662,7 @@
         <v>321</v>
       </c>
       <c r="Y42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -30675,7 +30675,7 @@
         <v>321</v>
       </c>
       <c r="C43" t="n">
-        <v>321</v>
+        <v>311.7961580087251</v>
       </c>
       <c r="D43" t="n">
         <v>321</v>
@@ -30696,7 +30696,7 @@
         <v>321</v>
       </c>
       <c r="J43" t="n">
-        <v>311.7961580087251</v>
+        <v>321</v>
       </c>
       <c r="K43" t="n">
         <v>321</v>
@@ -30833,10 +30833,10 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>131.8362718375286</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -30845,7 +30845,7 @@
         <v>321</v>
       </c>
       <c r="G45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>321</v>
@@ -30878,16 +30878,16 @@
         <v>77.25571792066825</v>
       </c>
       <c r="R45" t="n">
-        <v>131.8362718375428</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T45" t="n">
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V45" t="n">
         <v>321</v>
@@ -34743,16 +34743,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
         <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517586</v>
+        <v>374</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>374</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>59.25677413017286</v>
+        <v>306.1168901088537</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.6174062160025</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -34895,19 +34895,19 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>137.9156167349647</v>
       </c>
       <c r="I4" t="n">
-        <v>71.02753013108533</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4.06650298976183</v>
+        <v>4.066502989761812</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.86342193648881</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0.4418982775227391</v>
+      </c>
+      <c r="K5" t="n">
         <v>374</v>
       </c>
-      <c r="K5" t="n">
-        <v>53.18267336683419</v>
-      </c>
       <c r="L5" t="n">
-        <v>65.97780904522619</v>
+        <v>65.97780904522614</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>232.6343119585803</v>
       </c>
       <c r="O5" t="n">
         <v>374</v>
       </c>
       <c r="P5" t="n">
-        <v>374</v>
+        <v>59.8348696075598</v>
       </c>
       <c r="Q5" t="n">
-        <v>239.7284064768286</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,34 +35114,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>45.3808681752926</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.1436681420765</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.96055894966803</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>229.0064132323407</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>133.2680786578733</v>
       </c>
       <c r="L7" t="n">
         <v>4.334601350417529</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.89484816599702</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>190.7767449691521</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0518382337388</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,25 +35220,25 @@
         <v>0.4418982775227391</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>53.18267336683417</v>
       </c>
       <c r="L8" t="n">
         <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>358.2513224970163</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1956681143497576</v>
+        <v>245.4294476369722</v>
       </c>
       <c r="P8" t="n">
+        <v>59.8348696075598</v>
+      </c>
+      <c r="Q8" t="n">
         <v>374</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35305,7 +35305,7 @@
         <v>322.6623187449134</v>
       </c>
       <c r="M9" t="n">
-        <v>143.6300421645043</v>
+        <v>140.7874761356804</v>
       </c>
       <c r="N9" t="n">
         <v>192.8067010520511</v>
@@ -35314,7 +35314,7 @@
         <v>294.6804936008596</v>
       </c>
       <c r="P9" t="n">
-        <v>153.5399667877162</v>
+        <v>156.38253281654</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35369,19 +35369,19 @@
         <v>155.1436681420765</v>
       </c>
       <c r="H10" t="n">
-        <v>172.896283734447</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>229.0064132323407</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>13.29913402222095</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>133.2680786578733</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4.334601350417529</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,16 +35402,16 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.89484816599702</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0518382337388</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>149.9716249346423</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>84.03614450867852</v>
+        <v>401.3714762702401</v>
       </c>
       <c r="K11" t="n">
         <v>649</v>
       </c>
       <c r="L11" t="n">
-        <v>649.0000000000001</v>
+        <v>221.4063015075378</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>649</v>
       </c>
-      <c r="N11" t="n">
-        <v>171.1289849944258</v>
-      </c>
-      <c r="O11" t="n">
-        <v>166.1443867073146</v>
-      </c>
       <c r="P11" t="n">
-        <v>201.4682615673588</v>
+        <v>649</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35609,13 +35609,13 @@
         <v>97.82431652133221</v>
       </c>
       <c r="I13" t="n">
-        <v>154.0888007492626</v>
+        <v>163.2926427405375</v>
       </c>
       <c r="J13" t="n">
         <v>330.2256905083545</v>
       </c>
       <c r="K13" t="n">
-        <v>105.5975868545946</v>
+        <v>96.3937448633198</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>514.3408810948353</v>
+        <v>84.03614450867852</v>
       </c>
       <c r="K14" t="n">
-        <v>178.4687788944724</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
-        <v>221.4063015075377</v>
+        <v>538.7416332690995</v>
       </c>
       <c r="M14" t="n">
-        <v>245.8781964104238</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>166.1443867073146</v>
+        <v>649</v>
       </c>
       <c r="P14" t="n">
         <v>649</v>
       </c>
       <c r="Q14" t="n">
-        <v>594.5392331631938</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35840,7 +35840,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G16" t="n">
-        <v>67.38162942949037</v>
+        <v>76.58547142076505</v>
       </c>
       <c r="H16" t="n">
         <v>97.82431652133221</v>
@@ -35882,7 +35882,7 @@
         <v>113.6644498871849</v>
       </c>
       <c r="U16" t="n">
-        <v>170.0759365943945</v>
+        <v>160.8720946031197</v>
       </c>
       <c r="V16" t="n">
         <v>121.8296897837838</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>84.03614450867852</v>
+        <v>514.3408810948353</v>
       </c>
       <c r="K17" t="n">
-        <v>178.4687788944724</v>
+        <v>369.8862084680901</v>
       </c>
       <c r="L17" t="n">
+        <v>221.4063015075377</v>
+      </c>
+      <c r="M17" t="n">
         <v>649</v>
       </c>
-      <c r="M17" t="n">
-        <v>641.6602060999536</v>
-      </c>
       <c r="N17" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>166.1443867073146</v>
       </c>
       <c r="P17" t="n">
-        <v>201.4682615673588</v>
+        <v>649</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36074,7 +36074,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F19" t="n">
-        <v>46.61714403225807</v>
+        <v>37.4133020409833</v>
       </c>
       <c r="G19" t="n">
         <v>76.58547142076506</v>
@@ -36131,7 +36131,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y19" t="n">
-        <v>24.33080515926292</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="20">
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>514.3408810948353</v>
+        <v>84.03614450867852</v>
       </c>
       <c r="K20" t="n">
         <v>178.4687788944724</v>
@@ -36177,7 +36177,7 @@
         <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>44.40993484306523</v>
+        <v>649</v>
       </c>
       <c r="O20" t="n">
         <v>166.1443867073146</v>
@@ -36186,7 +36186,7 @@
         <v>201.4682615673588</v>
       </c>
       <c r="Q20" t="n">
-        <v>594.5392331631938</v>
+        <v>420.2539045924157</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36314,7 +36314,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G22" t="n">
-        <v>76.58547142076505</v>
+        <v>76.58547142076506</v>
       </c>
       <c r="H22" t="n">
         <v>97.82431652133221</v>
@@ -36323,7 +36323,7 @@
         <v>163.2926427405375</v>
       </c>
       <c r="J22" t="n">
-        <v>321.0218485170797</v>
+        <v>330.2256905083545</v>
       </c>
       <c r="K22" t="n">
         <v>105.5975868545946</v>
@@ -36356,7 +36356,7 @@
         <v>113.6644498871849</v>
       </c>
       <c r="U22" t="n">
-        <v>170.0759365943945</v>
+        <v>160.8720946031198</v>
       </c>
       <c r="V22" t="n">
         <v>121.8296897837838</v>
@@ -36405,22 +36405,22 @@
         <v>84.03614450867852</v>
       </c>
       <c r="K23" t="n">
+        <v>598.7226834868883</v>
+      </c>
+      <c r="L23" t="n">
+        <v>221.4063015075377</v>
+      </c>
+      <c r="M23" t="n">
         <v>649</v>
       </c>
-      <c r="L23" t="n">
-        <v>649.0000000000001</v>
-      </c>
-      <c r="M23" t="n">
-        <v>372.5972465617845</v>
-      </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O23" t="n">
         <v>166.1443867073146</v>
       </c>
       <c r="P23" t="n">
-        <v>649</v>
+        <v>201.4682615673588</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36557,7 +36557,7 @@
         <v>97.82431652133221</v>
       </c>
       <c r="I25" t="n">
-        <v>163.2926427405375</v>
+        <v>154.0888007492626</v>
       </c>
       <c r="J25" t="n">
         <v>330.2256905083545</v>
@@ -36605,7 +36605,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y25" t="n">
-        <v>24.33080515926292</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="26">
@@ -36648,16 +36648,16 @@
         <v>221.4063015075377</v>
       </c>
       <c r="M26" t="n">
-        <v>650</v>
+        <v>139.8261488266851</v>
       </c>
       <c r="N26" t="n">
         <v>650</v>
       </c>
       <c r="O26" t="n">
-        <v>166.1443867073146</v>
+        <v>650</v>
       </c>
       <c r="P26" t="n">
-        <v>623.6817621193707</v>
+        <v>650</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36882,10 +36882,10 @@
         <v>178.4687788944724</v>
       </c>
       <c r="L29" t="n">
-        <v>650</v>
+        <v>221.4063015075377</v>
       </c>
       <c r="M29" t="n">
-        <v>643.6198020595494</v>
+        <v>477.6742673888178</v>
       </c>
       <c r="N29" t="n">
         <v>650</v>
@@ -36897,7 +36897,7 @@
         <v>201.4682615673588</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>594.5392331631938</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37016,7 +37016,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>26.25993995316955</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E31" t="n">
         <v>40.01909516304346</v>
@@ -37073,7 +37073,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W31" t="n">
-        <v>94.62719016129032</v>
+        <v>85.42334817001542</v>
       </c>
       <c r="X31" t="n">
         <v>73.55635456989245</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>84.03614450867852</v>
+        <v>514.3408810948353</v>
       </c>
       <c r="K32" t="n">
-        <v>178.4687788944724</v>
+        <v>650</v>
       </c>
       <c r="L32" t="n">
-        <v>643.6198020595494</v>
+        <v>221.4063015075378</v>
       </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>650</v>
-      </c>
-      <c r="N32" t="n">
-        <v>650</v>
-      </c>
-      <c r="O32" t="n">
-        <v>166.1443867073146</v>
       </c>
       <c r="P32" t="n">
         <v>201.4682615673588</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>336.5219295676415</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37262,7 +37262,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G34" t="n">
-        <v>76.58547142076506</v>
+        <v>76.58547142076505</v>
       </c>
       <c r="H34" t="n">
         <v>97.82431652133221</v>
@@ -37304,10 +37304,10 @@
         <v>113.6644498871849</v>
       </c>
       <c r="U34" t="n">
-        <v>160.8720946031196</v>
+        <v>170.0759365943945</v>
       </c>
       <c r="V34" t="n">
-        <v>121.8296897837838</v>
+        <v>112.6258477925089</v>
       </c>
       <c r="W34" t="n">
         <v>94.62719016129032</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>84.03614450867852</v>
+        <v>172.639876977852</v>
       </c>
       <c r="K35" t="n">
-        <v>178.4687788944724</v>
+        <v>563</v>
       </c>
       <c r="L35" t="n">
-        <v>221.4063015075377</v>
+        <v>563</v>
       </c>
       <c r="M35" t="n">
         <v>563</v>
       </c>
       <c r="N35" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>166.1443867073146</v>
@@ -37371,7 +37371,7 @@
         <v>201.4682615673588</v>
       </c>
       <c r="Q35" t="n">
-        <v>251.7286520671637</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,10 +37435,10 @@
         <v>312.3220904898479</v>
       </c>
       <c r="L36" t="n">
-        <v>437.0842527071776</v>
+        <v>436.7028230419905</v>
       </c>
       <c r="M36" t="n">
-        <v>276.7736124993172</v>
+        <v>277.1550421645043</v>
       </c>
       <c r="N36" t="n">
         <v>329.8657104860133</v>
@@ -37487,7 +37487,7 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D37" t="n">
         <v>59.46378194444452</v>
@@ -37496,19 +37496,19 @@
         <v>64.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>100.585471420765</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>121.8243165213322</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>187.2926427405375</v>
       </c>
       <c r="J37" t="n">
-        <v>354.2256905083545</v>
+        <v>267.5499795193292</v>
       </c>
       <c r="K37" t="n">
         <v>129.5975868545946</v>
@@ -37544,16 +37544,16 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>14.56363748418644</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X37" t="n">
         <v>97.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37593,10 +37593,10 @@
         <v>178.4687788944724</v>
       </c>
       <c r="L38" t="n">
-        <v>221.4063015075377</v>
+        <v>562.9999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37605,10 +37605,10 @@
         <v>166.1443867073146</v>
       </c>
       <c r="P38" t="n">
-        <v>201.4682615673588</v>
+        <v>563</v>
       </c>
       <c r="Q38" t="n">
-        <v>384.4239154810068</v>
+        <v>244.2984785559034</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,13 +37672,13 @@
         <v>312.3220904898479</v>
       </c>
       <c r="L39" t="n">
-        <v>436.7028230419905</v>
+        <v>437.0842527071776</v>
       </c>
       <c r="M39" t="n">
         <v>277.1550421645043</v>
       </c>
       <c r="N39" t="n">
-        <v>329.8657104860133</v>
+        <v>329.484280820826</v>
       </c>
       <c r="O39" t="n">
         <v>420.0627105819917</v>
@@ -37724,7 +37724,7 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>59.46378194444452</v>
@@ -37736,16 +37736,16 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>100.585471420765</v>
+        <v>43.7189224866684</v>
       </c>
       <c r="H40" t="n">
         <v>121.8243165213322</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>187.2926427405375</v>
       </c>
       <c r="J40" t="n">
-        <v>9.225690508354518</v>
+        <v>354.2256905083545</v>
       </c>
       <c r="K40" t="n">
         <v>129.5975868545946</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>81.15981335887395</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>194.0759365943945</v>
       </c>
       <c r="V40" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>118.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>97.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>514.3408810948353</v>
+        <v>84.03614450867852</v>
       </c>
       <c r="K41" t="n">
         <v>178.4687788944724</v>
       </c>
       <c r="L41" t="n">
-        <v>221.4063015075377</v>
+        <v>473.1349535747011</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>563</v>
       </c>
       <c r="N41" t="n">
-        <v>384.4239154810065</v>
+        <v>563</v>
       </c>
       <c r="O41" t="n">
         <v>166.1443867073146</v>
@@ -37845,7 +37845,7 @@
         <v>201.4682615673588</v>
       </c>
       <c r="Q41" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>312.3220904898479</v>
       </c>
       <c r="L42" t="n">
-        <v>436.7028230420424</v>
+        <v>436.7028230420498</v>
       </c>
       <c r="M42" t="n">
         <v>277.1550421645043</v>
@@ -37961,7 +37961,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C43" t="n">
-        <v>48.27475335195533</v>
+        <v>39.07091136068037</v>
       </c>
       <c r="D43" t="n">
         <v>35.46378194444452</v>
@@ -37982,7 +37982,7 @@
         <v>163.2926427405375</v>
       </c>
       <c r="J43" t="n">
-        <v>321.0218485170797</v>
+        <v>330.2256905083545</v>
       </c>
       <c r="K43" t="n">
         <v>105.5975868545946</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>84.03614450867852</v>
+        <v>514.3408810948353</v>
       </c>
       <c r="K44" t="n">
-        <v>178.4687788944724</v>
+        <v>221.2989958830167</v>
       </c>
       <c r="L44" t="n">
-        <v>221.4063015075377</v>
+        <v>563</v>
       </c>
       <c r="M44" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>251.7286520671635</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>166.1443867073146</v>
@@ -38146,10 +38146,10 @@
         <v>312.3220904898479</v>
       </c>
       <c r="L45" t="n">
-        <v>437.0842527071776</v>
+        <v>436.7028230420572</v>
       </c>
       <c r="M45" t="n">
-        <v>276.7736124993691</v>
+        <v>277.1550421645043</v>
       </c>
       <c r="N45" t="n">
         <v>329.8657104860133</v>
